--- a/data_lake/macro/China/China PMI.xlsx
+++ b/data_lake/macro/China/China PMI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\China\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\China\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA1F1A69-C7E2-495D-A7F8-71F64C3F863E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43AFFC1-3416-4842-A358-54A2835B9CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
   </bookViews>
   <sheets>
     <sheet name="CPMINDX" sheetId="1" r:id="rId1"/>
@@ -89,24 +89,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -114,7 +114,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -122,7 +122,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -130,13 +130,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -159,56 +159,44 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -549,16 +537,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8641136A-8358-754A-BFC1-48B8F9996351}">
   <dimension ref="A1:G259"/>
-  <sheetFormatPr defaultColWidth="11.5" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9.296875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.26953125" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.296875" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.59765625" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.8984375" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.5" style="6"/>
+    <col min="6" max="6" width="8.6328125" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.90625" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.453125" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
@@ -6508,8 +6496,11 @@
       <c r="D259" s="9" t="s">
         <v>11</v>
       </c>
+      <c r="E259" s="10">
+        <v>50.3</v>
+      </c>
       <c r="F259" s="10">
-        <v>50.2</v>
+        <v>50.1</v>
       </c>
       <c r="G259" s="10">
         <v>50</v>
@@ -6528,5142 +6519,5146 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317C4CC0-835B-4324-B0A5-C9431E0655E3}">
   <dimension ref="A1:H235"/>
-  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.09765625" style="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.69921875" style="13" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.8984375" style="18" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.19921875" style="14" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.796875" style="16"/>
-    <col min="8" max="8" width="9.09765625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.08984375" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.90625" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1796875" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.81640625" style="13"/>
+    <col min="8" max="8" width="9.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="14" t="s">
         <v>4</v>
       </c>
       <c r="H1" s="12"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="13">
+      <c r="A2" s="7">
         <v>39083</v>
       </c>
-      <c r="B2" s="13">
+      <c r="B2" s="7">
         <v>39114</v>
       </c>
-      <c r="C2" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" s="16">
+      <c r="C2" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="13">
         <v>60.4</v>
       </c>
       <c r="H2" s="12"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A3" s="13">
+      <c r="A3" s="7">
         <v>39114</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="7">
         <v>39142</v>
       </c>
-      <c r="C3" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="16">
+      <c r="C3" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="13">
         <v>60.6</v>
       </c>
-      <c r="G3" s="16">
+      <c r="G3" s="13">
         <v>60.4</v>
       </c>
       <c r="H3" s="12"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A4" s="13">
+      <c r="A4" s="7">
         <v>39142</v>
       </c>
-      <c r="B4" s="13">
+      <c r="B4" s="7">
         <v>39173</v>
       </c>
-      <c r="C4" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="16">
+      <c r="C4" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="13">
         <v>58.2</v>
       </c>
-      <c r="G4" s="16">
+      <c r="G4" s="13">
         <v>60.6</v>
       </c>
       <c r="H4" s="12"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="13">
+      <c r="A5" s="7">
         <v>39173</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="7">
         <v>39203</v>
       </c>
-      <c r="C5" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="16">
+      <c r="C5" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="13">
         <v>60.4</v>
       </c>
-      <c r="G5" s="16">
+      <c r="G5" s="13">
         <v>58.2</v>
       </c>
       <c r="H5" s="12"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="13">
+      <c r="A6" s="7">
         <v>39203</v>
       </c>
-      <c r="B6" s="13">
+      <c r="B6" s="7">
         <v>39234</v>
       </c>
-      <c r="C6" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="16">
+      <c r="C6" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="13">
         <v>62.2</v>
       </c>
-      <c r="G6" s="16">
+      <c r="G6" s="13">
         <v>60.4</v>
       </c>
       <c r="H6" s="12"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="13">
+      <c r="A7" s="7">
         <v>39234</v>
       </c>
-      <c r="B7" s="13">
+      <c r="B7" s="7">
         <v>39264</v>
       </c>
-      <c r="C7" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="16">
+      <c r="C7" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" s="13">
         <v>60</v>
       </c>
-      <c r="G7" s="16">
+      <c r="G7" s="13">
         <v>62.2</v>
       </c>
       <c r="H7" s="12"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="13">
+      <c r="A8" s="7">
         <v>39264</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B8" s="7">
         <v>39295</v>
       </c>
-      <c r="C8" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" s="16">
+      <c r="C8" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="13">
         <v>59.4</v>
       </c>
-      <c r="G8" s="16">
+      <c r="G8" s="13">
         <v>60</v>
       </c>
       <c r="H8" s="12"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="13">
+      <c r="A9" s="7">
         <v>39295</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B9" s="7">
         <v>39326</v>
       </c>
-      <c r="C9" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" s="16">
+      <c r="C9" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="13">
         <v>61.7</v>
       </c>
-      <c r="G9" s="16">
+      <c r="G9" s="13">
         <v>59.4</v>
       </c>
       <c r="H9" s="12"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="13">
+      <c r="A10" s="7">
         <v>39326</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B10" s="7">
         <v>39356</v>
       </c>
-      <c r="C10" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E10" s="16">
+      <c r="C10" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="13">
         <v>61.9</v>
       </c>
-      <c r="G10" s="16">
+      <c r="G10" s="13">
         <v>61.7</v>
       </c>
       <c r="H10" s="12"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A11" s="13">
+      <c r="A11" s="7">
         <v>39356</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B11" s="7">
         <v>39387</v>
       </c>
-      <c r="C11" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="16">
+      <c r="C11" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="13">
         <v>61.4</v>
       </c>
-      <c r="G11" s="16">
+      <c r="G11" s="13">
         <v>61.9</v>
       </c>
       <c r="H11" s="12"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A12" s="13">
+      <c r="A12" s="7">
         <v>39387</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B12" s="7">
         <v>39417</v>
       </c>
-      <c r="C12" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D12" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E12" s="16">
+      <c r="C12" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" s="13">
         <v>60.6</v>
       </c>
-      <c r="G12" s="16">
+      <c r="G12" s="13">
         <v>61.4</v>
       </c>
       <c r="H12" s="12"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A13" s="13">
+      <c r="A13" s="7">
         <v>39417</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B13" s="7">
         <v>39448</v>
       </c>
-      <c r="C13" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E13" s="16">
+      <c r="C13" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" s="13">
         <v>60.2</v>
       </c>
-      <c r="G13" s="16">
+      <c r="G13" s="13">
         <v>60.6</v>
       </c>
       <c r="H13" s="12"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A14" s="13">
+      <c r="A14" s="7">
         <v>39448</v>
       </c>
-      <c r="B14" s="13">
+      <c r="B14" s="7">
         <v>39479</v>
       </c>
-      <c r="C14" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="16">
+      <c r="C14" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="13">
         <v>60.2</v>
       </c>
-      <c r="G14" s="16">
+      <c r="G14" s="13">
         <v>60.2</v>
       </c>
       <c r="H14" s="12"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A15" s="13">
+      <c r="A15" s="7">
         <v>39479</v>
       </c>
-      <c r="B15" s="13">
+      <c r="B15" s="7">
         <v>39508</v>
       </c>
-      <c r="C15" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="16">
+      <c r="C15" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E15" s="13">
         <v>59.3</v>
       </c>
-      <c r="G15" s="16">
+      <c r="G15" s="13">
         <v>60.2</v>
       </c>
       <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A16" s="13">
+      <c r="A16" s="7">
         <v>39508</v>
       </c>
-      <c r="B16" s="13">
+      <c r="B16" s="7">
         <v>39539</v>
       </c>
-      <c r="C16" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E16" s="16">
+      <c r="C16" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E16" s="13">
         <v>58.9</v>
       </c>
-      <c r="G16" s="16">
+      <c r="G16" s="13">
         <v>59.3</v>
       </c>
       <c r="H16" s="12"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A17" s="13">
+      <c r="A17" s="7">
         <v>39539</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="7">
         <v>39569</v>
       </c>
-      <c r="C17" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E17" s="16">
+      <c r="C17" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E17" s="13">
         <v>58.4</v>
       </c>
-      <c r="G17" s="16">
+      <c r="G17" s="13">
         <v>58.9</v>
       </c>
       <c r="H17" s="12"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A18" s="13">
+      <c r="A18" s="7">
         <v>39569</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="7">
         <v>39600</v>
       </c>
-      <c r="C18" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E18" s="16">
+      <c r="C18" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E18" s="13">
         <v>57.4</v>
       </c>
-      <c r="G18" s="16">
+      <c r="G18" s="13">
         <v>58.4</v>
       </c>
       <c r="H18" s="12"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A19" s="13">
+      <c r="A19" s="7">
         <v>39600</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="7">
         <v>39630</v>
       </c>
-      <c r="C19" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E19" s="16">
+      <c r="C19" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E19" s="13">
         <v>57.4</v>
       </c>
-      <c r="G19" s="16">
+      <c r="G19" s="13">
         <v>57.4</v>
       </c>
       <c r="H19" s="12"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="13">
+      <c r="A20" s="7">
         <v>39630</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="7">
         <v>39661</v>
       </c>
-      <c r="C20" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E20" s="16">
+      <c r="C20" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E20" s="13">
         <v>55.7</v>
       </c>
-      <c r="G20" s="16">
+      <c r="G20" s="13">
         <v>57.4</v>
       </c>
       <c r="H20" s="12"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A21" s="13">
+      <c r="A21" s="7">
         <v>39661</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="7">
         <v>39692</v>
       </c>
-      <c r="C21" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E21" s="16">
+      <c r="C21" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="13">
         <v>52.9</v>
       </c>
-      <c r="G21" s="16">
+      <c r="G21" s="13">
         <v>55.7</v>
       </c>
       <c r="H21" s="12"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A22" s="13">
+      <c r="A22" s="7">
         <v>39692</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="7">
         <v>39722</v>
       </c>
-      <c r="C22" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E22" s="16">
+      <c r="C22" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E22" s="13">
         <v>55</v>
       </c>
-      <c r="G22" s="16">
+      <c r="G22" s="13">
         <v>52.9</v>
       </c>
       <c r="H22" s="12"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A23" s="13">
+      <c r="A23" s="7">
         <v>39722</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="7">
         <v>39753</v>
       </c>
-      <c r="C23" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E23" s="16">
+      <c r="C23" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E23" s="13">
         <v>53.1</v>
       </c>
-      <c r="G23" s="16">
+      <c r="G23" s="13">
         <v>55</v>
       </c>
       <c r="H23" s="12"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A24" s="13">
+      <c r="A24" s="7">
         <v>39753</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="7">
         <v>39783</v>
       </c>
-      <c r="C24" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="16">
+      <c r="C24" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="13">
         <v>51.2</v>
       </c>
-      <c r="G24" s="16">
+      <c r="G24" s="13">
         <v>53.1</v>
       </c>
       <c r="H24" s="12"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A25" s="13">
+      <c r="A25" s="7">
         <v>39783</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="7">
         <v>39814</v>
       </c>
-      <c r="C25" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E25" s="16">
+      <c r="C25" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E25" s="13">
         <v>50.8</v>
       </c>
-      <c r="G25" s="16">
+      <c r="G25" s="13">
         <v>51.2</v>
       </c>
       <c r="H25" s="12"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A26" s="13">
+      <c r="A26" s="7">
         <v>39814</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="7">
         <v>39845</v>
       </c>
-      <c r="C26" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E26" s="16">
+      <c r="C26" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="13">
         <v>53.7</v>
       </c>
-      <c r="G26" s="16">
+      <c r="G26" s="13">
         <v>50.8</v>
       </c>
       <c r="H26" s="12"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A27" s="13">
+      <c r="A27" s="7">
         <v>39845</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="7">
         <v>39873</v>
       </c>
-      <c r="C27" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="16">
+      <c r="C27" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="13">
         <v>55.1</v>
       </c>
-      <c r="G27" s="16">
+      <c r="G27" s="13">
         <v>53.7</v>
       </c>
       <c r="H27" s="12"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A28" s="13">
+      <c r="A28" s="7">
         <v>39873</v>
       </c>
-      <c r="B28" s="13">
+      <c r="B28" s="7">
         <v>39904</v>
       </c>
-      <c r="C28" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E28" s="16">
+      <c r="C28" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E28" s="13">
         <v>54.4</v>
       </c>
-      <c r="G28" s="16">
+      <c r="G28" s="13">
         <v>55.1</v>
       </c>
       <c r="H28" s="12"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A29" s="13">
+      <c r="A29" s="7">
         <v>39904</v>
       </c>
-      <c r="B29" s="13">
+      <c r="B29" s="7">
         <v>39934</v>
       </c>
-      <c r="C29" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E29" s="16">
+      <c r="C29" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="13">
         <v>53.5</v>
       </c>
-      <c r="G29" s="16">
+      <c r="G29" s="13">
         <v>54.4</v>
       </c>
       <c r="H29" s="12"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A30" s="13">
+      <c r="A30" s="7">
         <v>39934</v>
       </c>
-      <c r="B30" s="13">
+      <c r="B30" s="7">
         <v>39965</v>
       </c>
-      <c r="C30" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D30" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="16">
+      <c r="C30" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="13">
         <v>54.9</v>
       </c>
-      <c r="G30" s="16">
+      <c r="G30" s="13">
         <v>53.5</v>
       </c>
       <c r="H30" s="12"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A31" s="13">
+      <c r="A31" s="7">
         <v>39965</v>
       </c>
-      <c r="B31" s="13">
+      <c r="B31" s="7">
         <v>39995</v>
       </c>
-      <c r="C31" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E31" s="16">
+      <c r="C31" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E31" s="13">
         <v>55.4</v>
       </c>
-      <c r="G31" s="16">
+      <c r="G31" s="13">
         <v>54.9</v>
       </c>
       <c r="H31" s="12"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A32" s="13">
+      <c r="A32" s="7">
         <v>39995</v>
       </c>
-      <c r="B32" s="13">
+      <c r="B32" s="7">
         <v>40026</v>
       </c>
-      <c r="C32" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="16">
+      <c r="C32" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E32" s="13">
         <v>57.3</v>
       </c>
-      <c r="G32" s="16">
+      <c r="G32" s="13">
         <v>55.4</v>
       </c>
       <c r="H32" s="12"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" s="13">
+      <c r="A33" s="7">
         <v>40026</v>
       </c>
-      <c r="B33" s="13">
+      <c r="B33" s="7">
         <v>40057</v>
       </c>
-      <c r="C33" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E33" s="16">
+      <c r="C33" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E33" s="13">
         <v>57.3</v>
       </c>
-      <c r="G33" s="16">
+      <c r="G33" s="13">
         <v>57.3</v>
       </c>
       <c r="H33" s="12"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A34" s="13">
+      <c r="A34" s="7">
         <v>40057</v>
       </c>
-      <c r="B34" s="13">
+      <c r="B34" s="7">
         <v>40087</v>
       </c>
-      <c r="C34" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E34" s="16">
+      <c r="C34" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E34" s="13">
         <v>57.9</v>
       </c>
-      <c r="G34" s="16">
+      <c r="G34" s="13">
         <v>57.3</v>
       </c>
       <c r="H34" s="12"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" s="13">
+      <c r="A35" s="7">
         <v>40087</v>
       </c>
-      <c r="B35" s="13">
+      <c r="B35" s="7">
         <v>40118</v>
       </c>
-      <c r="C35" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="16">
+      <c r="C35" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="13">
         <v>59.5</v>
       </c>
-      <c r="G35" s="16">
+      <c r="G35" s="13">
         <v>57.9</v>
       </c>
       <c r="H35" s="12"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" s="13">
+      <c r="A36" s="7">
         <v>40118</v>
       </c>
-      <c r="B36" s="13">
+      <c r="B36" s="7">
         <v>40148</v>
       </c>
-      <c r="C36" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E36" s="16">
+      <c r="C36" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D36" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E36" s="13">
         <v>58.4</v>
       </c>
-      <c r="G36" s="16">
+      <c r="G36" s="13">
         <v>59.5</v>
       </c>
       <c r="H36" s="12"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A37" s="13">
+      <c r="A37" s="7">
         <v>40148</v>
       </c>
-      <c r="B37" s="13">
+      <c r="B37" s="7">
         <v>40179</v>
       </c>
-      <c r="C37" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D37" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E37" s="16">
+      <c r="C37" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E37" s="13">
         <v>58.8</v>
       </c>
-      <c r="G37" s="16">
+      <c r="G37" s="13">
         <v>58.4</v>
       </c>
       <c r="H37" s="12"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A38" s="13">
+      <c r="A38" s="7">
         <v>40179</v>
       </c>
-      <c r="B38" s="13">
+      <c r="B38" s="7">
         <v>40210</v>
       </c>
-      <c r="C38" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D38" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E38" s="16">
+      <c r="C38" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D38" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E38" s="13">
         <v>58.1</v>
       </c>
-      <c r="G38" s="16">
+      <c r="G38" s="13">
         <v>58.8</v>
       </c>
       <c r="H38" s="12"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A39" s="13">
+      <c r="A39" s="7">
         <v>40210</v>
       </c>
-      <c r="B39" s="13">
+      <c r="B39" s="7">
         <v>40238</v>
       </c>
-      <c r="C39" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E39" s="16">
+      <c r="C39" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E39" s="13">
         <v>57</v>
       </c>
-      <c r="G39" s="16">
+      <c r="G39" s="13">
         <v>58.1</v>
       </c>
       <c r="H39" s="12"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A40" s="13">
+      <c r="A40" s="7">
         <v>40238</v>
       </c>
-      <c r="B40" s="13">
+      <c r="B40" s="7">
         <v>40269</v>
       </c>
-      <c r="C40" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E40" s="16">
+      <c r="C40" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D40" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E40" s="13">
         <v>57.3</v>
       </c>
-      <c r="G40" s="16">
+      <c r="G40" s="13">
         <v>57</v>
       </c>
       <c r="H40" s="12"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A41" s="13">
+      <c r="A41" s="7">
         <v>40269</v>
       </c>
-      <c r="B41" s="13">
+      <c r="B41" s="7">
         <v>40299</v>
       </c>
-      <c r="C41" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E41" s="16">
+      <c r="C41" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D41" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E41" s="13">
         <v>57.8</v>
       </c>
-      <c r="G41" s="16">
+      <c r="G41" s="13">
         <v>57.3</v>
       </c>
       <c r="H41" s="12"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A42" s="13">
+      <c r="A42" s="7">
         <v>40299</v>
       </c>
-      <c r="B42" s="13">
+      <c r="B42" s="7">
         <v>40330</v>
       </c>
-      <c r="C42" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="16">
+      <c r="C42" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E42" s="13">
         <v>58.1</v>
       </c>
-      <c r="G42" s="16">
+      <c r="G42" s="13">
         <v>57.8</v>
       </c>
       <c r="H42" s="12"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A43" s="13">
+      <c r="A43" s="7">
         <v>40330</v>
       </c>
-      <c r="B43" s="13">
+      <c r="B43" s="7">
         <v>40360</v>
       </c>
-      <c r="C43" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="16">
+      <c r="C43" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E43" s="13">
         <v>58.8</v>
       </c>
-      <c r="G43" s="16">
+      <c r="G43" s="13">
         <v>58.1</v>
       </c>
       <c r="H43" s="12"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A44" s="13">
+      <c r="A44" s="7">
         <v>40360</v>
       </c>
-      <c r="B44" s="13">
+      <c r="B44" s="7">
         <v>40391</v>
       </c>
-      <c r="C44" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="16">
+      <c r="C44" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D44" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E44" s="13">
         <v>57.1</v>
       </c>
-      <c r="G44" s="16">
+      <c r="G44" s="13">
         <v>58.8</v>
       </c>
       <c r="H44" s="12"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A45" s="13">
+      <c r="A45" s="7">
         <v>40391</v>
       </c>
-      <c r="B45" s="13">
+      <c r="B45" s="7">
         <v>40422</v>
       </c>
-      <c r="C45" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="16">
+      <c r="C45" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D45" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E45" s="13">
         <v>58</v>
       </c>
-      <c r="G45" s="16">
+      <c r="G45" s="13">
         <v>57.1</v>
       </c>
       <c r="H45" s="12"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A46" s="13">
+      <c r="A46" s="7">
         <v>40422</v>
       </c>
-      <c r="B46" s="13">
+      <c r="B46" s="7">
         <v>40452</v>
       </c>
-      <c r="C46" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E46" s="16">
+      <c r="C46" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D46" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E46" s="13">
         <v>57.9</v>
       </c>
-      <c r="G46" s="16">
+      <c r="G46" s="13">
         <v>58</v>
       </c>
       <c r="H46" s="12"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A47" s="13">
+      <c r="A47" s="7">
         <v>40452</v>
       </c>
-      <c r="B47" s="13">
+      <c r="B47" s="7">
         <v>40483</v>
       </c>
-      <c r="C47" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E47" s="16">
+      <c r="C47" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D47" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E47" s="13">
         <v>57.4</v>
       </c>
-      <c r="G47" s="16">
+      <c r="G47" s="13">
         <v>57.9</v>
       </c>
       <c r="H47" s="12"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A48" s="13">
+      <c r="A48" s="7">
         <v>40483</v>
       </c>
-      <c r="B48" s="13">
+      <c r="B48" s="7">
         <v>40513</v>
       </c>
-      <c r="C48" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E48" s="16">
+      <c r="C48" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D48" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E48" s="13">
         <v>58.9</v>
       </c>
-      <c r="G48" s="16">
+      <c r="G48" s="13">
         <v>57.4</v>
       </c>
       <c r="H48" s="12"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A49" s="13">
+      <c r="A49" s="7">
         <v>40513</v>
       </c>
-      <c r="B49" s="13">
+      <c r="B49" s="7">
         <v>40544</v>
       </c>
-      <c r="C49" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="16">
+      <c r="C49" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D49" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="13">
         <v>58.8</v>
       </c>
-      <c r="G49" s="16">
+      <c r="G49" s="13">
         <v>58.9</v>
       </c>
       <c r="H49" s="12"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="13">
+      <c r="A50" s="7">
         <v>40544</v>
       </c>
-      <c r="B50" s="13">
+      <c r="B50" s="7">
         <v>40575</v>
       </c>
-      <c r="C50" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E50" s="16">
+      <c r="C50" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D50" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E50" s="13">
         <v>57.2</v>
       </c>
-      <c r="G50" s="16">
+      <c r="G50" s="13">
         <v>58.8</v>
       </c>
       <c r="H50" s="12"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" s="13">
+      <c r="A51" s="7">
         <v>40575</v>
       </c>
-      <c r="B51" s="13">
+      <c r="B51" s="7">
         <v>40603</v>
       </c>
-      <c r="C51" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E51" s="16">
+      <c r="C51" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D51" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E51" s="13">
         <v>57</v>
       </c>
-      <c r="G51" s="16">
+      <c r="G51" s="13">
         <v>57.2</v>
       </c>
       <c r="H51" s="12"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52" s="13">
+      <c r="A52" s="7">
         <v>40603</v>
       </c>
-      <c r="B52" s="13">
+      <c r="B52" s="7">
         <v>40634</v>
       </c>
-      <c r="C52" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E52" s="16">
+      <c r="C52" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D52" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E52" s="13">
         <v>59.2</v>
       </c>
-      <c r="G52" s="16">
+      <c r="G52" s="13">
         <v>57</v>
       </c>
       <c r="H52" s="12"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53" s="13">
+      <c r="A53" s="7">
         <v>40634</v>
       </c>
-      <c r="B53" s="13">
+      <c r="B53" s="7">
         <v>40664</v>
       </c>
-      <c r="C53" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E53" s="16">
+      <c r="C53" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D53" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E53" s="13">
         <v>58.2</v>
       </c>
-      <c r="G53" s="16">
+      <c r="G53" s="13">
         <v>59.2</v>
       </c>
       <c r="H53" s="12"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A54" s="13">
+      <c r="A54" s="7">
         <v>40664</v>
       </c>
-      <c r="B54" s="13">
+      <c r="B54" s="7">
         <v>40695</v>
       </c>
-      <c r="C54" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E54" s="16">
+      <c r="C54" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D54" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E54" s="13">
         <v>58.7</v>
       </c>
-      <c r="G54" s="16">
+      <c r="G54" s="13">
         <v>58.2</v>
       </c>
       <c r="H54" s="12"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="13">
+      <c r="A55" s="7">
         <v>40695</v>
       </c>
-      <c r="B55" s="13">
+      <c r="B55" s="7">
         <v>40725</v>
       </c>
-      <c r="C55" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E55" s="16">
+      <c r="C55" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D55" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E55" s="13">
         <v>56.6</v>
       </c>
-      <c r="G55" s="16">
+      <c r="G55" s="13">
         <v>58.7</v>
       </c>
       <c r="H55" s="12"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" s="13">
+      <c r="A56" s="7">
         <v>40725</v>
       </c>
-      <c r="B56" s="13">
+      <c r="B56" s="7">
         <v>40756</v>
       </c>
-      <c r="C56" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E56" s="16">
+      <c r="C56" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D56" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E56" s="13">
         <v>57.3</v>
       </c>
-      <c r="G56" s="16">
+      <c r="G56" s="13">
         <v>56.6</v>
       </c>
       <c r="H56" s="12"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57" s="13">
+      <c r="A57" s="7">
         <v>40756</v>
       </c>
-      <c r="B57" s="13">
+      <c r="B57" s="7">
         <v>40787</v>
       </c>
-      <c r="C57" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E57" s="16">
+      <c r="C57" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D57" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E57" s="13">
         <v>57.1</v>
       </c>
-      <c r="G57" s="16">
+      <c r="G57" s="13">
         <v>57.3</v>
       </c>
       <c r="H57" s="12"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58" s="13">
+      <c r="A58" s="7">
         <v>40787</v>
       </c>
-      <c r="B58" s="13">
+      <c r="B58" s="7">
         <v>40817</v>
       </c>
-      <c r="C58" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E58" s="16">
+      <c r="C58" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D58" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E58" s="13">
         <v>55.8</v>
       </c>
-      <c r="G58" s="16">
+      <c r="G58" s="13">
         <v>57.1</v>
       </c>
       <c r="H58" s="12"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="13">
+      <c r="A59" s="7">
         <v>40817</v>
       </c>
-      <c r="B59" s="13">
+      <c r="B59" s="7">
         <v>40848</v>
       </c>
-      <c r="C59" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E59" s="16">
+      <c r="C59" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D59" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E59" s="13">
         <v>55.5</v>
       </c>
-      <c r="G59" s="16">
+      <c r="G59" s="13">
         <v>55.8</v>
       </c>
       <c r="H59" s="12"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60" s="13">
+      <c r="A60" s="7">
         <v>40848</v>
       </c>
-      <c r="B60" s="13">
+      <c r="B60" s="7">
         <v>40878</v>
       </c>
-      <c r="C60" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E60" s="16">
+      <c r="C60" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D60" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E60" s="13">
         <v>55.9</v>
       </c>
-      <c r="G60" s="16">
+      <c r="G60" s="13">
         <v>55.5</v>
       </c>
       <c r="H60" s="12"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A61" s="13">
+      <c r="A61" s="7">
         <v>40878</v>
       </c>
-      <c r="B61" s="13">
+      <c r="B61" s="7">
         <v>40909</v>
       </c>
-      <c r="C61" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D61" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E61" s="16">
+      <c r="C61" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D61" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E61" s="13">
         <v>56.3</v>
       </c>
-      <c r="G61" s="16">
+      <c r="G61" s="13">
         <v>55.9</v>
       </c>
       <c r="H61" s="12"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A62" s="13">
+      <c r="A62" s="7">
         <v>40909</v>
       </c>
-      <c r="B62" s="13">
+      <c r="B62" s="7">
         <v>40940</v>
       </c>
-      <c r="C62" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E62" s="16">
+      <c r="C62" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E62" s="13">
         <v>55.7</v>
       </c>
-      <c r="G62" s="16">
+      <c r="G62" s="13">
         <v>56.3</v>
       </c>
       <c r="H62" s="12"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="13">
+      <c r="A63" s="7">
         <v>40940</v>
       </c>
-      <c r="B63" s="13">
+      <c r="B63" s="7">
         <v>40969</v>
       </c>
-      <c r="C63" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E63" s="16">
+      <c r="C63" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D63" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E63" s="13">
         <v>57.3</v>
       </c>
-      <c r="G63" s="16">
+      <c r="G63" s="13">
         <v>55.7</v>
       </c>
       <c r="H63" s="12"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" s="13">
+      <c r="A64" s="7">
         <v>40969</v>
       </c>
-      <c r="B64" s="13">
+      <c r="B64" s="7">
         <v>41000</v>
       </c>
-      <c r="C64" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D64" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E64" s="16">
+      <c r="C64" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D64" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E64" s="13">
         <v>58</v>
       </c>
-      <c r="G64" s="16">
+      <c r="G64" s="13">
         <v>57.3</v>
       </c>
       <c r="H64" s="12"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A65" s="13">
+      <c r="A65" s="7">
         <v>41000</v>
       </c>
-      <c r="B65" s="13">
+      <c r="B65" s="7">
         <v>41030</v>
       </c>
-      <c r="C65" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D65" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E65" s="16">
+      <c r="C65" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D65" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E65" s="13">
         <v>56.1</v>
       </c>
-      <c r="G65" s="16">
+      <c r="G65" s="13">
         <v>58</v>
       </c>
       <c r="H65" s="12"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A66" s="13">
+      <c r="A66" s="7">
         <v>41030</v>
       </c>
-      <c r="B66" s="13">
+      <c r="B66" s="7">
         <v>41061</v>
       </c>
-      <c r="C66" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E66" s="16">
+      <c r="C66" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D66" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" s="13">
         <v>55.2</v>
       </c>
-      <c r="G66" s="16">
+      <c r="G66" s="13">
         <v>56.1</v>
       </c>
       <c r="H66" s="12"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A67" s="13">
+      <c r="A67" s="7">
         <v>41061</v>
       </c>
-      <c r="B67" s="13">
+      <c r="B67" s="7">
         <v>41091</v>
       </c>
-      <c r="C67" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D67" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E67" s="16">
+      <c r="C67" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D67" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E67" s="13">
         <v>56.7</v>
       </c>
-      <c r="G67" s="16">
+      <c r="G67" s="13">
         <v>55.2</v>
       </c>
       <c r="H67" s="12"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A68" s="13">
+      <c r="A68" s="7">
         <v>41091</v>
       </c>
-      <c r="B68" s="13">
+      <c r="B68" s="7">
         <v>41124</v>
       </c>
-      <c r="C68" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E68" s="16">
+      <c r="C68" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D68" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" s="13">
         <v>55.6</v>
       </c>
-      <c r="G68" s="16">
+      <c r="G68" s="13">
         <v>56.7</v>
       </c>
       <c r="H68" s="12"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A69" s="13">
+      <c r="A69" s="7">
         <v>41122</v>
       </c>
-      <c r="B69" s="13">
+      <c r="B69" s="7">
         <v>41155</v>
       </c>
-      <c r="C69" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E69" s="16">
+      <c r="C69" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D69" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E69" s="13">
         <v>56.3</v>
       </c>
-      <c r="G69" s="16">
+      <c r="G69" s="13">
         <v>55.6</v>
       </c>
       <c r="H69" s="12"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A70" s="13">
+      <c r="A70" s="7">
         <v>41153</v>
       </c>
-      <c r="B70" s="13">
+      <c r="B70" s="7">
         <v>41185</v>
       </c>
-      <c r="C70" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E70" s="16">
+      <c r="C70" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D70" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E70" s="13">
         <v>53.7</v>
       </c>
-      <c r="G70" s="16">
+      <c r="G70" s="13">
         <v>56.3</v>
       </c>
       <c r="H70" s="12"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A71" s="13">
+      <c r="A71" s="7">
         <v>41183</v>
       </c>
-      <c r="B71" s="13">
+      <c r="B71" s="7">
         <v>41216</v>
       </c>
-      <c r="C71" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E71" s="16">
+      <c r="C71" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D71" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E71" s="13">
         <v>55.5</v>
       </c>
-      <c r="G71" s="16">
+      <c r="G71" s="13">
         <v>53.7</v>
       </c>
       <c r="H71" s="12"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A72" s="13">
+      <c r="A72" s="7">
         <v>41214</v>
       </c>
-      <c r="B72" s="13">
+      <c r="B72" s="7">
         <v>41246</v>
       </c>
-      <c r="C72" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D72" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E72" s="16">
+      <c r="C72" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D72" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E72" s="13">
         <v>55.6</v>
       </c>
-      <c r="G72" s="16">
+      <c r="G72" s="13">
         <v>55.5</v>
       </c>
       <c r="H72" s="12"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A73" s="13">
+      <c r="A73" s="7">
         <v>41244</v>
       </c>
-      <c r="B73" s="13">
+      <c r="B73" s="7">
         <v>41277</v>
       </c>
-      <c r="C73" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E73" s="16">
+      <c r="C73" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D73" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E73" s="13">
         <v>56.1</v>
       </c>
-      <c r="G73" s="16">
+      <c r="G73" s="13">
         <v>55.6</v>
       </c>
       <c r="H73" s="12"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A74" s="13">
+      <c r="A74" s="7">
         <v>41275</v>
       </c>
-      <c r="B74" s="13">
+      <c r="B74" s="7">
         <v>41308</v>
       </c>
-      <c r="C74" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E74" s="16">
+      <c r="C74" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D74" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E74" s="13">
         <v>56.2</v>
       </c>
-      <c r="G74" s="16">
+      <c r="G74" s="13">
         <v>56.1</v>
       </c>
       <c r="H74" s="12"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A75" s="13">
+      <c r="A75" s="7">
         <v>41306</v>
       </c>
-      <c r="B75" s="13">
+      <c r="B75" s="7">
         <v>41336</v>
       </c>
-      <c r="C75" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D75" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E75" s="16">
+      <c r="C75" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D75" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E75" s="13">
         <v>54.5</v>
       </c>
-      <c r="G75" s="16">
+      <c r="G75" s="13">
         <v>56.2</v>
       </c>
       <c r="H75" s="12"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A76" s="13">
+      <c r="A76" s="7">
         <v>41334</v>
       </c>
-      <c r="B76" s="13">
+      <c r="B76" s="7">
         <v>41367</v>
       </c>
-      <c r="C76" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D76" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E76" s="16">
+      <c r="C76" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D76" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E76" s="13">
         <v>55.6</v>
       </c>
-      <c r="G76" s="16">
+      <c r="G76" s="13">
         <v>54.5</v>
       </c>
       <c r="H76" s="12"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A77" s="13">
+      <c r="A77" s="7">
         <v>41365</v>
       </c>
-      <c r="B77" s="13">
+      <c r="B77" s="7">
         <v>41397</v>
       </c>
-      <c r="C77" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D77" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E77" s="16">
+      <c r="C77" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D77" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E77" s="13">
         <v>54.5</v>
       </c>
-      <c r="G77" s="16">
+      <c r="G77" s="13">
         <v>55.6</v>
       </c>
       <c r="H77" s="12"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A78" s="13">
+      <c r="A78" s="7">
         <v>41395</v>
       </c>
-      <c r="B78" s="13">
+      <c r="B78" s="7">
         <v>41428</v>
       </c>
-      <c r="C78" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D78" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E78" s="16">
+      <c r="C78" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D78" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E78" s="13">
         <v>54.3</v>
       </c>
-      <c r="G78" s="16">
+      <c r="G78" s="13">
         <v>54.5</v>
       </c>
       <c r="H78" s="12"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A79" s="13">
+      <c r="A79" s="7">
         <v>41426</v>
       </c>
-      <c r="B79" s="13">
+      <c r="B79" s="7">
         <v>41458</v>
       </c>
-      <c r="C79" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D79" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E79" s="16">
+      <c r="C79" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D79" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E79" s="13">
         <v>53.9</v>
       </c>
-      <c r="G79" s="16">
+      <c r="G79" s="13">
         <v>54.3</v>
       </c>
       <c r="H79" s="12"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A80" s="13">
+      <c r="A80" s="7">
         <v>41456</v>
       </c>
-      <c r="B80" s="13">
+      <c r="B80" s="7">
         <v>41489</v>
       </c>
-      <c r="C80" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D80" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E80" s="16">
+      <c r="C80" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D80" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E80" s="13">
         <v>54.1</v>
       </c>
-      <c r="G80" s="16">
+      <c r="G80" s="13">
         <v>53.9</v>
       </c>
       <c r="H80" s="12"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A81" s="13">
+      <c r="A81" s="7">
         <v>41487</v>
       </c>
-      <c r="B81" s="13">
+      <c r="B81" s="7">
         <v>41520</v>
       </c>
-      <c r="C81" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D81" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E81" s="16">
+      <c r="C81" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D81" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E81" s="13">
         <v>53.9</v>
       </c>
-      <c r="G81" s="16">
+      <c r="G81" s="13">
         <v>54.1</v>
       </c>
       <c r="H81" s="12"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A82" s="13">
+      <c r="A82" s="7">
         <v>41518</v>
       </c>
-      <c r="B82" s="13">
+      <c r="B82" s="7">
         <v>41550</v>
       </c>
-      <c r="C82" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D82" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E82" s="16">
+      <c r="C82" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D82" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E82" s="13">
         <v>55.4</v>
       </c>
-      <c r="G82" s="16">
+      <c r="G82" s="13">
         <v>53.9</v>
       </c>
       <c r="H82" s="12"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A83" s="13">
+      <c r="A83" s="7">
         <v>41548</v>
       </c>
-      <c r="B83" s="13">
+      <c r="B83" s="7">
         <v>41581</v>
       </c>
-      <c r="C83" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D83" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E83" s="16">
+      <c r="C83" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D83" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E83" s="13">
         <v>56.3</v>
       </c>
-      <c r="G83" s="16">
+      <c r="G83" s="13">
         <v>55.4</v>
       </c>
       <c r="H83" s="12"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A84" s="13">
+      <c r="A84" s="7">
         <v>41579</v>
       </c>
-      <c r="B84" s="13">
+      <c r="B84" s="7">
         <v>41611</v>
       </c>
-      <c r="C84" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D84" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E84" s="16">
+      <c r="C84" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D84" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E84" s="13">
         <v>56</v>
       </c>
-      <c r="G84" s="16">
+      <c r="G84" s="13">
         <v>56.3</v>
       </c>
       <c r="H84" s="12"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A85" s="13">
+      <c r="A85" s="7">
         <v>41609</v>
       </c>
-      <c r="B85" s="13">
+      <c r="B85" s="7">
         <v>41642</v>
       </c>
-      <c r="C85" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D85" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E85" s="16">
+      <c r="C85" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E85" s="13">
         <v>54.6</v>
       </c>
-      <c r="G85" s="16">
+      <c r="G85" s="13">
         <v>56</v>
       </c>
       <c r="H85" s="12"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A86" s="13">
+      <c r="A86" s="7">
         <v>41640</v>
       </c>
-      <c r="B86" s="13">
+      <c r="B86" s="7">
         <v>41673</v>
       </c>
-      <c r="C86" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D86" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E86" s="16">
+      <c r="C86" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D86" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E86" s="13">
         <v>53.4</v>
       </c>
-      <c r="G86" s="16">
+      <c r="G86" s="13">
         <v>54.6</v>
       </c>
       <c r="H86" s="12"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A87" s="13">
+      <c r="A87" s="7">
         <v>41671</v>
       </c>
-      <c r="B87" s="13">
+      <c r="B87" s="7">
         <v>41701</v>
       </c>
-      <c r="C87" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D87" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E87" s="16">
+      <c r="C87" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D87" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" s="13">
         <v>55</v>
       </c>
-      <c r="G87" s="16">
+      <c r="G87" s="13">
         <v>53.4</v>
       </c>
       <c r="H87" s="12"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A88" s="13">
+      <c r="A88" s="7">
         <v>41699</v>
       </c>
-      <c r="B88" s="13">
+      <c r="B88" s="7">
         <v>41732</v>
       </c>
-      <c r="C88" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D88" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E88" s="16">
+      <c r="C88" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D88" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E88" s="13">
         <v>54.5</v>
       </c>
-      <c r="G88" s="16">
+      <c r="G88" s="13">
         <v>55</v>
       </c>
       <c r="H88" s="12"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A89" s="13">
+      <c r="A89" s="7">
         <v>41730</v>
       </c>
-      <c r="B89" s="13">
+      <c r="B89" s="7">
         <v>41762</v>
       </c>
-      <c r="C89" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D89" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E89" s="16">
+      <c r="C89" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D89" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E89" s="13">
         <v>54.8</v>
       </c>
-      <c r="G89" s="16">
+      <c r="G89" s="13">
         <v>54.5</v>
       </c>
       <c r="H89" s="12"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A90" s="13">
+      <c r="A90" s="7">
         <v>41760</v>
       </c>
-      <c r="B90" s="13">
+      <c r="B90" s="7">
         <v>41793</v>
       </c>
-      <c r="C90" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D90" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E90" s="16">
+      <c r="C90" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D90" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E90" s="13">
         <v>55.5</v>
       </c>
-      <c r="G90" s="16">
+      <c r="G90" s="13">
         <v>54.8</v>
       </c>
       <c r="H90" s="12"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A91" s="13">
+      <c r="A91" s="7">
         <v>41791</v>
       </c>
-      <c r="B91" s="13">
+      <c r="B91" s="7">
         <v>41823</v>
       </c>
-      <c r="C91" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D91" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E91" s="16">
+      <c r="C91" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D91" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E91" s="13">
         <v>55</v>
       </c>
-      <c r="G91" s="16">
+      <c r="G91" s="13">
         <v>55.5</v>
       </c>
       <c r="H91" s="12"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A92" s="13">
+      <c r="A92" s="7">
         <v>41821</v>
       </c>
-      <c r="B92" s="13">
+      <c r="B92" s="7">
         <v>41854</v>
       </c>
-      <c r="C92" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D92" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E92" s="16">
+      <c r="C92" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D92" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E92" s="13">
         <v>54.2</v>
       </c>
-      <c r="G92" s="16">
+      <c r="G92" s="13">
         <v>55</v>
       </c>
       <c r="H92" s="12"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A93" s="13">
+      <c r="A93" s="7">
         <v>41852</v>
       </c>
-      <c r="B93" s="13">
+      <c r="B93" s="7">
         <v>41885</v>
       </c>
-      <c r="C93" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D93" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E93" s="16">
+      <c r="C93" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E93" s="13">
         <v>54.4</v>
       </c>
-      <c r="G93" s="16">
+      <c r="G93" s="13">
         <v>54.2</v>
       </c>
       <c r="H93" s="12"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A94" s="13">
+      <c r="A94" s="7">
         <v>41883</v>
       </c>
-      <c r="B94" s="13">
+      <c r="B94" s="7">
         <v>41915</v>
       </c>
-      <c r="C94" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D94" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E94" s="16">
+      <c r="C94" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D94" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E94" s="13">
         <v>54</v>
       </c>
-      <c r="G94" s="16">
+      <c r="G94" s="13">
         <v>54.4</v>
       </c>
       <c r="H94" s="12"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A95" s="13">
+      <c r="A95" s="7">
         <v>41913</v>
       </c>
-      <c r="B95" s="13">
+      <c r="B95" s="7">
         <v>41946</v>
       </c>
-      <c r="C95" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D95" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E95" s="16">
+      <c r="C95" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D95" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E95" s="13">
         <v>53.8</v>
       </c>
-      <c r="G95" s="16">
+      <c r="G95" s="13">
         <v>54</v>
       </c>
       <c r="H95" s="12"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A96" s="13">
+      <c r="A96" s="7">
         <v>41944</v>
       </c>
-      <c r="B96" s="13">
+      <c r="B96" s="7">
         <v>41976</v>
       </c>
-      <c r="C96" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D96" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E96" s="16">
+      <c r="C96" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D96" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E96" s="13">
         <v>53.9</v>
       </c>
-      <c r="G96" s="16">
+      <c r="G96" s="13">
         <v>53.8</v>
       </c>
       <c r="H96" s="12"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A97" s="13">
+      <c r="A97" s="7">
         <v>41974</v>
       </c>
-      <c r="B97" s="13">
+      <c r="B97" s="7">
         <v>42005</v>
       </c>
-      <c r="C97" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D97" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E97" s="16">
+      <c r="C97" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D97" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" s="13">
         <v>54.1</v>
       </c>
-      <c r="G97" s="16">
+      <c r="G97" s="13">
         <v>53.9</v>
       </c>
       <c r="H97" s="12"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A98" s="13">
+      <c r="A98" s="7">
         <v>42005</v>
       </c>
-      <c r="B98" s="13">
+      <c r="B98" s="7">
         <v>42036</v>
       </c>
-      <c r="C98" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D98" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E98" s="16">
+      <c r="C98" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D98" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E98" s="13">
         <v>53.7</v>
       </c>
-      <c r="G98" s="16">
+      <c r="G98" s="13">
         <v>54.1</v>
       </c>
       <c r="H98" s="12"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A99" s="13">
+      <c r="A99" s="7">
         <v>42036</v>
       </c>
-      <c r="B99" s="13">
+      <c r="B99" s="7">
         <v>42064</v>
       </c>
-      <c r="C99" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D99" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E99" s="16">
+      <c r="C99" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D99" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E99" s="13">
         <v>53.9</v>
       </c>
-      <c r="G99" s="16">
+      <c r="G99" s="13">
         <v>53.7</v>
       </c>
       <c r="H99" s="12"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A100" s="13">
+      <c r="A100" s="7">
         <v>42064</v>
       </c>
-      <c r="B100" s="13">
+      <c r="B100" s="7">
         <v>42095</v>
       </c>
-      <c r="C100" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D100" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E100" s="16">
+      <c r="C100" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D100" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E100" s="13">
         <v>53.7</v>
       </c>
-      <c r="G100" s="16">
+      <c r="G100" s="13">
         <v>53.9</v>
       </c>
       <c r="H100" s="12"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A101" s="13">
+      <c r="A101" s="7">
         <v>42095</v>
       </c>
-      <c r="B101" s="13">
+      <c r="B101" s="7">
         <v>42125</v>
       </c>
-      <c r="C101" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D101" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E101" s="16">
+      <c r="C101" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D101" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E101" s="13">
         <v>53.4</v>
       </c>
-      <c r="G101" s="16">
+      <c r="G101" s="13">
         <v>53.7</v>
       </c>
       <c r="H101" s="12"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A102" s="13">
+      <c r="A102" s="7">
         <v>42125</v>
       </c>
-      <c r="B102" s="13">
+      <c r="B102" s="7">
         <v>42156</v>
       </c>
-      <c r="C102" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D102" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E102" s="16">
+      <c r="C102" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D102" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E102" s="13">
         <v>53.2</v>
       </c>
-      <c r="G102" s="16">
+      <c r="G102" s="13">
         <v>53.4</v>
       </c>
       <c r="H102" s="12"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A103" s="13">
+      <c r="A103" s="7">
         <v>42156</v>
       </c>
-      <c r="B103" s="13">
+      <c r="B103" s="7">
         <v>42186</v>
       </c>
-      <c r="C103" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D103" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E103" s="16">
+      <c r="C103" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D103" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E103" s="13">
         <v>53.8</v>
       </c>
-      <c r="G103" s="16">
+      <c r="G103" s="13">
         <v>53.2</v>
       </c>
       <c r="H103" s="12"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A104" s="13">
+      <c r="A104" s="7">
         <v>42186</v>
       </c>
-      <c r="B104" s="13">
+      <c r="B104" s="7">
         <v>42217</v>
       </c>
-      <c r="C104" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D104" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E104" s="16">
+      <c r="C104" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D104" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E104" s="13">
         <v>53.9</v>
       </c>
-      <c r="G104" s="16">
+      <c r="G104" s="13">
         <v>53.8</v>
       </c>
       <c r="H104" s="12"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A105" s="13">
+      <c r="A105" s="7">
         <v>42217</v>
       </c>
-      <c r="B105" s="13">
+      <c r="B105" s="7">
         <v>42248</v>
       </c>
-      <c r="C105" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D105" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E105" s="16">
+      <c r="C105" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E105" s="13">
         <v>53.4</v>
       </c>
-      <c r="G105" s="16">
+      <c r="G105" s="13">
         <v>53.9</v>
       </c>
       <c r="H105" s="12"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A106" s="13">
+      <c r="A106" s="7">
         <v>42248</v>
       </c>
-      <c r="B106" s="13">
+      <c r="B106" s="7">
         <v>42278</v>
       </c>
-      <c r="C106" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D106" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E106" s="16">
+      <c r="C106" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D106" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E106" s="13">
         <v>53.4</v>
       </c>
-      <c r="G106" s="16">
+      <c r="G106" s="13">
         <v>53.4</v>
       </c>
       <c r="H106" s="12"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A107" s="13">
+      <c r="A107" s="7">
         <v>42278</v>
       </c>
-      <c r="B107" s="13">
+      <c r="B107" s="7">
         <v>42309</v>
       </c>
-      <c r="C107" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D107" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E107" s="16">
+      <c r="C107" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D107" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" s="13">
         <v>53.1</v>
       </c>
-      <c r="G107" s="16">
+      <c r="G107" s="13">
         <v>53.4</v>
       </c>
       <c r="H107" s="12"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A108" s="13">
+      <c r="A108" s="7">
         <v>42309</v>
       </c>
-      <c r="B108" s="13">
+      <c r="B108" s="7">
         <v>42339</v>
       </c>
-      <c r="C108" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D108" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E108" s="16">
+      <c r="C108" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D108" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E108" s="13">
         <v>53.6</v>
       </c>
-      <c r="G108" s="16">
+      <c r="G108" s="13">
         <v>53.1</v>
       </c>
       <c r="H108" s="12"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A109" s="13">
+      <c r="A109" s="7">
         <v>42339</v>
       </c>
-      <c r="B109" s="13">
+      <c r="B109" s="7">
         <v>42370</v>
       </c>
-      <c r="C109" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D109" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E109" s="16">
+      <c r="C109" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D109" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E109" s="13">
         <v>54.4</v>
       </c>
-      <c r="G109" s="16">
+      <c r="G109" s="13">
         <v>53.6</v>
       </c>
       <c r="H109" s="12"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A110" s="13">
+      <c r="A110" s="7">
         <v>42370</v>
       </c>
-      <c r="B110" s="13">
+      <c r="B110" s="7">
         <v>42401</v>
       </c>
-      <c r="C110" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D110" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E110" s="16">
+      <c r="C110" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D110" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" s="13">
         <v>53.5</v>
       </c>
-      <c r="G110" s="16">
+      <c r="G110" s="13">
         <v>54.4</v>
       </c>
       <c r="H110" s="12"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A111" s="13">
+      <c r="A111" s="7">
         <v>42401</v>
       </c>
-      <c r="B111" s="13">
+      <c r="B111" s="7">
         <v>42430</v>
       </c>
-      <c r="C111" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D111" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E111" s="16">
+      <c r="C111" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D111" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" s="13">
         <v>52.7</v>
       </c>
-      <c r="G111" s="16">
+      <c r="G111" s="13">
         <v>53.5</v>
       </c>
       <c r="H111" s="12"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A112" s="13">
+      <c r="A112" s="7">
         <v>42430</v>
       </c>
-      <c r="B112" s="13">
+      <c r="B112" s="7">
         <v>42461</v>
       </c>
-      <c r="C112" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D112" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E112" s="16">
+      <c r="C112" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D112" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E112" s="13">
         <v>53.8</v>
       </c>
-      <c r="G112" s="16">
+      <c r="G112" s="13">
         <v>52.7</v>
       </c>
       <c r="H112" s="12"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A113" s="13">
+      <c r="A113" s="7">
         <v>42461</v>
       </c>
-      <c r="B113" s="13">
+      <c r="B113" s="7">
         <v>42491</v>
       </c>
-      <c r="C113" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D113" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E113" s="16">
+      <c r="C113" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D113" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E113" s="13">
         <v>53.5</v>
       </c>
-      <c r="G113" s="16">
+      <c r="G113" s="13">
         <v>53.8</v>
       </c>
       <c r="H113" s="12"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A114" s="13">
+      <c r="A114" s="7">
         <v>42491</v>
       </c>
-      <c r="B114" s="13">
+      <c r="B114" s="7">
         <v>42522</v>
       </c>
-      <c r="C114" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D114" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E114" s="16">
+      <c r="C114" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D114" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E114" s="13">
         <v>53.1</v>
       </c>
-      <c r="G114" s="16">
+      <c r="G114" s="13">
         <v>53.5</v>
       </c>
       <c r="H114" s="12"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A115" s="13">
+      <c r="A115" s="7">
         <v>42522</v>
       </c>
-      <c r="B115" s="13">
+      <c r="B115" s="7">
         <v>42552</v>
       </c>
-      <c r="C115" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D115" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E115" s="16">
+      <c r="C115" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D115" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E115" s="13">
         <v>53.7</v>
       </c>
-      <c r="G115" s="16">
+      <c r="G115" s="13">
         <v>53.1</v>
       </c>
       <c r="H115" s="12"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A116" s="13">
+      <c r="A116" s="7">
         <v>42552</v>
       </c>
-      <c r="B116" s="13">
+      <c r="B116" s="7">
         <v>42583</v>
       </c>
-      <c r="C116" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D116" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E116" s="16">
+      <c r="C116" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D116" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E116" s="13">
         <v>53.9</v>
       </c>
-      <c r="G116" s="16">
+      <c r="G116" s="13">
         <v>53.7</v>
       </c>
       <c r="H116" s="12"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A117" s="13">
+      <c r="A117" s="7">
         <v>42583</v>
       </c>
-      <c r="B117" s="13">
+      <c r="B117" s="7">
         <v>42614</v>
       </c>
-      <c r="C117" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D117" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E117" s="16">
+      <c r="C117" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D117" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E117" s="13">
         <v>53.5</v>
       </c>
-      <c r="G117" s="16">
+      <c r="G117" s="13">
         <v>53.9</v>
       </c>
       <c r="H117" s="12"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A118" s="13">
+      <c r="A118" s="7">
         <v>42614</v>
       </c>
-      <c r="B118" s="13">
+      <c r="B118" s="7">
         <v>42644</v>
       </c>
-      <c r="C118" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D118" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E118" s="16">
+      <c r="C118" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D118" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="13">
         <v>53.7</v>
       </c>
-      <c r="G118" s="16">
+      <c r="G118" s="13">
         <v>53.5</v>
       </c>
       <c r="H118" s="12"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A119" s="13">
+      <c r="A119" s="7">
         <v>42644</v>
       </c>
-      <c r="B119" s="13">
+      <c r="B119" s="7">
         <v>42675</v>
       </c>
-      <c r="C119" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D119" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E119" s="16">
+      <c r="C119" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D119" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E119" s="13">
         <v>54</v>
       </c>
-      <c r="G119" s="16">
+      <c r="G119" s="13">
         <v>53.7</v>
       </c>
       <c r="H119" s="12"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A120" s="13">
+      <c r="A120" s="7">
         <v>42675</v>
       </c>
-      <c r="B120" s="13">
+      <c r="B120" s="7">
         <v>42705</v>
       </c>
-      <c r="C120" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D120" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E120" s="16">
+      <c r="C120" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D120" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E120" s="13">
         <v>54.7</v>
       </c>
-      <c r="G120" s="16">
+      <c r="G120" s="13">
         <v>54</v>
       </c>
       <c r="H120" s="12"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A121" s="13">
+      <c r="A121" s="7">
         <v>42705</v>
       </c>
-      <c r="B121" s="13">
+      <c r="B121" s="7">
         <v>42736</v>
       </c>
-      <c r="C121" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D121" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E121" s="16">
+      <c r="C121" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D121" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E121" s="13">
         <v>54.5</v>
       </c>
-      <c r="G121" s="16">
+      <c r="G121" s="13">
         <v>54.7</v>
       </c>
       <c r="H121" s="12"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A122" s="13">
+      <c r="A122" s="7">
         <v>42736</v>
       </c>
-      <c r="B122" s="13">
+      <c r="B122" s="7">
         <v>42767</v>
       </c>
-      <c r="C122" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D122" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E122" s="16">
+      <c r="C122" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D122" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E122" s="13">
         <v>54.6</v>
       </c>
-      <c r="G122" s="16">
+      <c r="G122" s="13">
         <v>54.5</v>
       </c>
       <c r="H122" s="12"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A123" s="13">
+      <c r="A123" s="7">
         <v>42767</v>
       </c>
-      <c r="B123" s="13">
+      <c r="B123" s="7">
         <v>42795</v>
       </c>
-      <c r="C123" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D123" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E123" s="16">
+      <c r="C123" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D123" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E123" s="13">
         <v>54.2</v>
       </c>
-      <c r="G123" s="16">
+      <c r="G123" s="13">
         <v>54.6</v>
       </c>
       <c r="H123" s="12"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A124" s="13">
+      <c r="A124" s="7">
         <v>42795</v>
       </c>
-      <c r="B124" s="13">
+      <c r="B124" s="7">
         <v>42825</v>
       </c>
-      <c r="C124" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D124" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E124" s="16">
+      <c r="C124" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E124" s="13">
         <v>55.1</v>
       </c>
-      <c r="G124" s="16">
+      <c r="G124" s="13">
         <v>54.2</v>
       </c>
       <c r="H124" s="12"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A125" s="13">
+      <c r="A125" s="7">
         <v>42826</v>
       </c>
-      <c r="B125" s="13">
+      <c r="B125" s="7">
         <v>42855</v>
       </c>
-      <c r="C125" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D125" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E125" s="16">
+      <c r="C125" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D125" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E125" s="13">
         <v>54</v>
       </c>
-      <c r="G125" s="16">
+      <c r="G125" s="13">
         <v>55.1</v>
       </c>
       <c r="H125" s="12"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A126" s="13">
+      <c r="A126" s="7">
         <v>42856</v>
       </c>
-      <c r="B126" s="13">
+      <c r="B126" s="7">
         <v>42886</v>
       </c>
-      <c r="C126" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D126" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E126" s="16">
+      <c r="C126" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D126" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E126" s="13">
         <v>54.5</v>
       </c>
-      <c r="G126" s="16">
+      <c r="G126" s="13">
         <v>54</v>
       </c>
       <c r="H126" s="12"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A127" s="13">
+      <c r="A127" s="7">
         <v>42887</v>
       </c>
-      <c r="B127" s="13">
+      <c r="B127" s="7">
         <v>42916</v>
       </c>
-      <c r="C127" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D127" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E127" s="16">
+      <c r="C127" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D127" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E127" s="13">
         <v>54.9</v>
       </c>
-      <c r="G127" s="16">
+      <c r="G127" s="13">
         <v>54.5</v>
       </c>
       <c r="H127" s="12"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A128" s="13">
+      <c r="A128" s="7">
         <v>42917</v>
       </c>
-      <c r="B128" s="13">
+      <c r="B128" s="7">
         <v>42947</v>
       </c>
-      <c r="C128" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D128" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E128" s="16">
+      <c r="C128" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D128" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E128" s="13">
         <v>54.5</v>
       </c>
-      <c r="G128" s="16">
+      <c r="G128" s="13">
         <v>54.9</v>
       </c>
       <c r="H128" s="12"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A129" s="13">
+      <c r="A129" s="7">
         <v>42948</v>
       </c>
-      <c r="B129" s="13">
+      <c r="B129" s="7">
         <v>42978</v>
       </c>
-      <c r="C129" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D129" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E129" s="16">
+      <c r="C129" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D129" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" s="13">
         <v>53.4</v>
       </c>
-      <c r="G129" s="16">
+      <c r="G129" s="13">
         <v>54.5</v>
       </c>
       <c r="H129" s="12"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A130" s="13">
+      <c r="A130" s="7">
         <v>42979</v>
       </c>
-      <c r="B130" s="13">
+      <c r="B130" s="7">
         <v>43008</v>
       </c>
-      <c r="C130" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D130" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E130" s="16">
+      <c r="C130" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D130" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E130" s="13">
         <v>55.4</v>
       </c>
-      <c r="G130" s="16">
+      <c r="G130" s="13">
         <v>53.4</v>
       </c>
       <c r="H130" s="12"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A131" s="13">
+      <c r="A131" s="7">
         <v>43009</v>
       </c>
-      <c r="B131" s="13">
+      <c r="B131" s="7">
         <v>43039</v>
       </c>
-      <c r="C131" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D131" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E131" s="16">
+      <c r="C131" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D131" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" s="13">
         <v>54.3</v>
       </c>
-      <c r="G131" s="16">
+      <c r="G131" s="13">
         <v>55.4</v>
       </c>
       <c r="H131" s="12"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A132" s="13">
+      <c r="A132" s="7">
         <v>43040</v>
       </c>
-      <c r="B132" s="13">
+      <c r="B132" s="7">
         <v>43069</v>
       </c>
-      <c r="C132" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D132" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E132" s="16">
+      <c r="C132" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D132" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E132" s="13">
         <v>54.8</v>
       </c>
-      <c r="G132" s="16">
+      <c r="G132" s="13">
         <v>54.3</v>
       </c>
       <c r="H132" s="12"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A133" s="13">
+      <c r="A133" s="7">
         <v>43070</v>
       </c>
-      <c r="B133" s="13">
+      <c r="B133" s="7">
         <v>43100</v>
       </c>
-      <c r="C133" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D133" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E133" s="16">
+      <c r="C133" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D133" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E133" s="13">
         <v>55</v>
       </c>
-      <c r="G133" s="16">
+      <c r="G133" s="13">
         <v>54.8</v>
       </c>
       <c r="H133" s="12"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A134" s="13">
+      <c r="A134" s="7">
         <v>43101</v>
       </c>
-      <c r="B134" s="13">
+      <c r="B134" s="7">
         <v>43131</v>
       </c>
-      <c r="C134" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D134" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E134" s="16">
+      <c r="C134" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D134" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E134" s="13">
         <v>55.3</v>
       </c>
-      <c r="F134" s="16">
+      <c r="F134" s="13">
         <v>55</v>
       </c>
-      <c r="G134" s="16">
+      <c r="G134" s="13">
         <v>55</v>
       </c>
       <c r="H134" s="12"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A135" s="13">
+      <c r="A135" s="7">
         <v>43132</v>
       </c>
-      <c r="B135" s="13">
+      <c r="B135" s="7">
         <v>43159</v>
       </c>
-      <c r="C135" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D135" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E135" s="16">
+      <c r="C135" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D135" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E135" s="13">
         <v>54.4</v>
       </c>
-      <c r="F135" s="16">
+      <c r="F135" s="13">
         <v>55</v>
       </c>
-      <c r="G135" s="16">
+      <c r="G135" s="13">
         <v>55.3</v>
       </c>
       <c r="H135" s="12"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A136" s="13">
+      <c r="A136" s="7">
         <v>43160</v>
       </c>
-      <c r="B136" s="13">
+      <c r="B136" s="7">
         <v>43190</v>
       </c>
-      <c r="C136" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D136" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E136" s="16">
+      <c r="C136" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D136" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E136" s="13">
         <v>54.6</v>
       </c>
-      <c r="G136" s="16">
+      <c r="G136" s="13">
         <v>54.4</v>
       </c>
       <c r="H136" s="12"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A137" s="13">
+      <c r="A137" s="7">
         <v>43191</v>
       </c>
-      <c r="B137" s="13">
+      <c r="B137" s="7">
         <v>43220</v>
       </c>
-      <c r="C137" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D137" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E137" s="16">
+      <c r="C137" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D137" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E137" s="13">
         <v>54.8</v>
       </c>
-      <c r="F137" s="16">
+      <c r="F137" s="13">
         <v>54.6</v>
       </c>
-      <c r="G137" s="16">
+      <c r="G137" s="13">
         <v>54.6</v>
       </c>
       <c r="H137" s="12"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A138" s="13">
+      <c r="A138" s="7">
         <v>43221</v>
       </c>
-      <c r="B138" s="13">
+      <c r="B138" s="7">
         <v>43251</v>
       </c>
-      <c r="C138" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D138" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E138" s="16">
+      <c r="C138" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D138" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E138" s="13">
         <v>54.9</v>
       </c>
-      <c r="F138" s="16">
+      <c r="F138" s="13">
         <v>54.8</v>
       </c>
-      <c r="G138" s="16">
+      <c r="G138" s="13">
         <v>54.8</v>
       </c>
       <c r="H138" s="12"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A139" s="13">
+      <c r="A139" s="7">
         <v>43252</v>
       </c>
-      <c r="B139" s="13">
+      <c r="B139" s="7">
         <v>43281</v>
       </c>
-      <c r="C139" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D139" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E139" s="16">
+      <c r="C139" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D139" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E139" s="13">
         <v>55</v>
       </c>
-      <c r="F139" s="16">
+      <c r="F139" s="13">
         <v>54.7</v>
       </c>
-      <c r="G139" s="16">
+      <c r="G139" s="13">
         <v>54.9</v>
       </c>
       <c r="H139" s="12"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A140" s="13">
+      <c r="A140" s="7">
         <v>43282</v>
       </c>
-      <c r="B140" s="13">
+      <c r="B140" s="7">
         <v>43312</v>
       </c>
-      <c r="C140" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D140" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E140" s="16">
+      <c r="C140" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D140" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E140" s="13">
         <v>54</v>
       </c>
-      <c r="F140" s="16">
+      <c r="F140" s="13">
         <v>55</v>
       </c>
-      <c r="G140" s="16">
+      <c r="G140" s="13">
         <v>55</v>
       </c>
       <c r="H140" s="12"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A141" s="13">
+      <c r="A141" s="7">
         <v>43313</v>
       </c>
-      <c r="B141" s="13">
+      <c r="B141" s="7">
         <v>43343</v>
       </c>
-      <c r="C141" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D141" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E141" s="16">
+      <c r="C141" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D141" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E141" s="13">
         <v>54.2</v>
       </c>
-      <c r="F141" s="16">
+      <c r="F141" s="13">
         <v>53.8</v>
       </c>
-      <c r="G141" s="16">
+      <c r="G141" s="13">
         <v>54</v>
       </c>
       <c r="H141" s="12"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A142" s="13">
+      <c r="A142" s="7">
         <v>43344</v>
       </c>
-      <c r="B142" s="13">
+      <c r="B142" s="7">
         <v>43373</v>
       </c>
-      <c r="C142" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D142" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E142" s="16">
+      <c r="C142" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D142" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E142" s="13">
         <v>54.9</v>
       </c>
-      <c r="G142" s="16">
+      <c r="G142" s="13">
         <v>54.2</v>
       </c>
       <c r="H142" s="12"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A143" s="13">
+      <c r="A143" s="7">
         <v>43374</v>
       </c>
-      <c r="B143" s="13">
+      <c r="B143" s="7">
         <v>43404</v>
       </c>
-      <c r="C143" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D143" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E143" s="16">
+      <c r="C143" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D143" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E143" s="13">
         <v>53.9</v>
       </c>
-      <c r="F143" s="16">
+      <c r="F143" s="13">
         <v>54.9</v>
       </c>
-      <c r="G143" s="16">
+      <c r="G143" s="13">
         <v>54.9</v>
       </c>
       <c r="H143" s="12"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A144" s="13">
+      <c r="A144" s="7">
         <v>43405</v>
       </c>
-      <c r="B144" s="13">
+      <c r="B144" s="7">
         <v>43434</v>
       </c>
-      <c r="C144" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D144" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E144" s="16">
+      <c r="C144" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D144" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E144" s="13">
         <v>53.4</v>
       </c>
-      <c r="F144" s="16">
+      <c r="F144" s="13">
         <v>53.8</v>
       </c>
-      <c r="G144" s="16">
+      <c r="G144" s="13">
         <v>53.9</v>
       </c>
       <c r="H144" s="12"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A145" s="13">
+      <c r="A145" s="7">
         <v>43435</v>
       </c>
-      <c r="B145" s="13">
+      <c r="B145" s="7">
         <v>43465</v>
       </c>
-      <c r="C145" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D145" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E145" s="16">
+      <c r="C145" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D145" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E145" s="13">
         <v>53.8</v>
       </c>
-      <c r="F145" s="16">
+      <c r="F145" s="13">
         <v>53.2</v>
       </c>
-      <c r="G145" s="16">
+      <c r="G145" s="13">
         <v>53.4</v>
       </c>
       <c r="H145" s="12"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A146" s="13">
+      <c r="A146" s="7">
         <v>43466</v>
       </c>
-      <c r="B146" s="13">
+      <c r="B146" s="7">
         <v>43496</v>
       </c>
-      <c r="C146" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D146" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E146" s="16">
+      <c r="C146" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D146" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E146" s="13">
         <v>54.7</v>
       </c>
-      <c r="F146" s="16">
+      <c r="F146" s="13">
         <v>53.9</v>
       </c>
-      <c r="G146" s="16">
+      <c r="G146" s="13">
         <v>53.8</v>
       </c>
       <c r="H146" s="12"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A147" s="13">
+      <c r="A147" s="7">
         <v>43497</v>
       </c>
-      <c r="B147" s="13">
+      <c r="B147" s="7">
         <v>43524</v>
       </c>
-      <c r="C147" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D147" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E147" s="16">
+      <c r="C147" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D147" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E147" s="13">
         <v>54.3</v>
       </c>
-      <c r="F147" s="16">
+      <c r="F147" s="13">
         <v>54.5</v>
       </c>
-      <c r="G147" s="16">
+      <c r="G147" s="13">
         <v>54.7</v>
       </c>
       <c r="H147" s="12"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A148" s="13">
+      <c r="A148" s="7">
         <v>43525</v>
       </c>
-      <c r="B148" s="13">
+      <c r="B148" s="7">
         <v>43555</v>
       </c>
-      <c r="C148" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D148" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E148" s="16">
+      <c r="C148" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D148" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E148" s="13">
         <v>54.8</v>
       </c>
-      <c r="F148" s="16">
+      <c r="F148" s="13">
         <v>54.5</v>
       </c>
-      <c r="G148" s="16">
+      <c r="G148" s="13">
         <v>54.3</v>
       </c>
       <c r="H148" s="12"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A149" s="13">
+      <c r="A149" s="7">
         <v>43556</v>
       </c>
-      <c r="B149" s="13">
+      <c r="B149" s="7">
         <v>43585</v>
       </c>
-      <c r="C149" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D149" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E149" s="16">
+      <c r="C149" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D149" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E149" s="13">
         <v>54.3</v>
       </c>
-      <c r="F149" s="16">
+      <c r="F149" s="13">
         <v>55</v>
       </c>
-      <c r="G149" s="16">
+      <c r="G149" s="13">
         <v>54.8</v>
       </c>
       <c r="H149" s="12"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A150" s="13">
+      <c r="A150" s="7">
         <v>43586</v>
       </c>
-      <c r="B150" s="13">
+      <c r="B150" s="7">
         <v>43616</v>
       </c>
-      <c r="C150" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D150" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E150" s="16">
+      <c r="C150" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D150" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E150" s="13">
         <v>54.3</v>
       </c>
-      <c r="F150" s="16">
+      <c r="F150" s="13">
         <v>54.3</v>
       </c>
-      <c r="G150" s="16">
+      <c r="G150" s="13">
         <v>54.3</v>
       </c>
       <c r="H150" s="12"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A151" s="13">
+      <c r="A151" s="7">
         <v>43617</v>
       </c>
-      <c r="B151" s="13">
+      <c r="B151" s="7">
         <v>43646</v>
       </c>
-      <c r="C151" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D151" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E151" s="16">
+      <c r="C151" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D151" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E151" s="13">
         <v>54.2</v>
       </c>
-      <c r="F151" s="16">
+      <c r="F151" s="13">
         <v>54.1</v>
       </c>
-      <c r="G151" s="16">
+      <c r="G151" s="13">
         <v>54.3</v>
       </c>
       <c r="H151" s="12"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A152" s="13">
+      <c r="A152" s="7">
         <v>43647</v>
       </c>
-      <c r="B152" s="13">
+      <c r="B152" s="7">
         <v>43677</v>
       </c>
-      <c r="C152" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D152" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E152" s="16">
+      <c r="C152" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D152" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E152" s="13">
         <v>53.7</v>
       </c>
-      <c r="F152" s="16">
+      <c r="F152" s="13">
         <v>54</v>
       </c>
-      <c r="G152" s="16">
+      <c r="G152" s="13">
         <v>54.2</v>
       </c>
       <c r="H152" s="12"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A153" s="13">
+      <c r="A153" s="7">
         <v>43678</v>
       </c>
-      <c r="B153" s="13">
+      <c r="B153" s="7">
         <v>43708</v>
       </c>
-      <c r="C153" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D153" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E153" s="16">
+      <c r="C153" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D153" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E153" s="13">
         <v>53.8</v>
       </c>
-      <c r="F153" s="16">
+      <c r="F153" s="13">
         <v>53.6</v>
       </c>
-      <c r="G153" s="16">
+      <c r="G153" s="13">
         <v>53.7</v>
       </c>
       <c r="H153" s="12"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A154" s="13">
+      <c r="A154" s="7">
         <v>43709</v>
       </c>
-      <c r="B154" s="13">
+      <c r="B154" s="7">
         <v>43738</v>
       </c>
-      <c r="C154" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D154" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E154" s="16">
+      <c r="C154" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D154" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E154" s="13">
         <v>53.7</v>
       </c>
-      <c r="F154" s="16">
+      <c r="F154" s="13">
         <v>54.2</v>
       </c>
-      <c r="G154" s="16">
+      <c r="G154" s="13">
         <v>53.8</v>
       </c>
       <c r="H154" s="12"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A155" s="13">
+      <c r="A155" s="7">
         <v>43739</v>
       </c>
-      <c r="B155" s="13">
+      <c r="B155" s="7">
         <v>43769</v>
       </c>
-      <c r="C155" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D155" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E155" s="16">
+      <c r="C155" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D155" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E155" s="13">
         <v>52.8</v>
       </c>
-      <c r="F155" s="16">
+      <c r="F155" s="13">
         <v>53.7</v>
       </c>
-      <c r="G155" s="16">
+      <c r="G155" s="13">
         <v>53.7</v>
       </c>
       <c r="H155" s="12"/>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A156" s="13">
+      <c r="A156" s="7">
         <v>43770</v>
       </c>
-      <c r="B156" s="13">
+      <c r="B156" s="7">
         <v>43799</v>
       </c>
-      <c r="C156" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D156" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E156" s="16">
+      <c r="C156" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D156" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" s="13">
         <v>54.4</v>
       </c>
-      <c r="G156" s="16">
+      <c r="G156" s="13">
         <v>52.8</v>
       </c>
       <c r="H156" s="12"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A157" s="13">
+      <c r="A157" s="7">
         <v>43800</v>
       </c>
-      <c r="B157" s="13">
+      <c r="B157" s="7">
         <v>43830</v>
       </c>
-      <c r="C157" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D157" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E157" s="16">
+      <c r="C157" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D157" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E157" s="13">
         <v>53.5</v>
       </c>
-      <c r="G157" s="16">
+      <c r="G157" s="13">
         <v>54.4</v>
       </c>
       <c r="H157" s="12"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A158" s="13">
+      <c r="A158" s="7">
         <v>43831</v>
       </c>
-      <c r="B158" s="13">
+      <c r="B158" s="7">
         <v>43861</v>
       </c>
-      <c r="C158" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D158" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E158" s="16">
+      <c r="C158" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D158" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E158" s="13">
         <v>54.1</v>
       </c>
-      <c r="G158" s="16">
+      <c r="G158" s="13">
         <v>53.5</v>
       </c>
       <c r="H158" s="12"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A159" s="13">
+      <c r="A159" s="7">
         <v>43862</v>
       </c>
-      <c r="B159" s="13">
+      <c r="B159" s="7">
         <v>43890</v>
       </c>
-      <c r="C159" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D159" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E159" s="16">
+      <c r="C159" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D159" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E159" s="13">
         <v>29.6</v>
       </c>
-      <c r="G159" s="16">
+      <c r="G159" s="13">
         <v>54.1</v>
       </c>
       <c r="H159" s="12"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A160" s="13">
+      <c r="A160" s="7">
         <v>43891</v>
       </c>
-      <c r="B160" s="13">
+      <c r="B160" s="7">
         <v>43921</v>
       </c>
-      <c r="C160" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D160" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E160" s="16">
+      <c r="C160" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D160" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" s="13">
         <v>52.3</v>
       </c>
-      <c r="G160" s="16">
+      <c r="G160" s="13">
         <v>29.6</v>
       </c>
       <c r="H160" s="12"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A161" s="13">
+      <c r="A161" s="7">
         <v>43922</v>
       </c>
-      <c r="B161" s="13">
+      <c r="B161" s="7">
         <v>43951</v>
       </c>
-      <c r="C161" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D161" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E161" s="16">
+      <c r="C161" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D161" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E161" s="13">
         <v>53.2</v>
       </c>
-      <c r="G161" s="16">
+      <c r="G161" s="13">
         <v>52.3</v>
       </c>
       <c r="H161" s="12"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A162" s="13">
+      <c r="A162" s="7">
         <v>43952</v>
       </c>
-      <c r="B162" s="13">
+      <c r="B162" s="7">
         <v>43982</v>
       </c>
-      <c r="C162" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D162" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E162" s="16">
+      <c r="C162" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D162" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E162" s="13">
         <v>53.6</v>
       </c>
-      <c r="G162" s="16">
+      <c r="G162" s="13">
         <v>53.2</v>
       </c>
       <c r="H162" s="12"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A163" s="13">
+      <c r="A163" s="7">
         <v>43983</v>
       </c>
-      <c r="B163" s="13">
+      <c r="B163" s="7">
         <v>44012</v>
       </c>
-      <c r="C163" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D163" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E163" s="16">
+      <c r="C163" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D163" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E163" s="13">
         <v>54.4</v>
       </c>
-      <c r="G163" s="16">
+      <c r="G163" s="13">
         <v>53.6</v>
       </c>
       <c r="H163" s="12"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A164" s="13">
+      <c r="A164" s="7">
         <v>44013</v>
       </c>
-      <c r="B164" s="13">
+      <c r="B164" s="7">
         <v>44043</v>
       </c>
-      <c r="C164" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D164" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E164" s="16">
+      <c r="C164" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D164" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E164" s="13">
         <v>54.2</v>
       </c>
-      <c r="G164" s="16">
+      <c r="G164" s="13">
         <v>54.4</v>
       </c>
       <c r="H164" s="12"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A165" s="13">
+      <c r="A165" s="7">
         <v>44044</v>
       </c>
-      <c r="B165" s="13">
+      <c r="B165" s="7">
         <v>44074</v>
       </c>
-      <c r="C165" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D165" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E165" s="16">
+      <c r="C165" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D165" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E165" s="13">
         <v>55.2</v>
       </c>
-      <c r="G165" s="16">
+      <c r="G165" s="13">
         <v>54.2</v>
       </c>
       <c r="H165" s="12"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A166" s="13">
+      <c r="A166" s="7">
         <v>44075</v>
       </c>
-      <c r="B166" s="13">
+      <c r="B166" s="7">
         <v>44104</v>
       </c>
-      <c r="C166" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D166" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E166" s="16">
+      <c r="C166" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D166" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E166" s="13">
         <v>55.9</v>
       </c>
-      <c r="G166" s="16">
+      <c r="G166" s="13">
         <v>55.2</v>
       </c>
       <c r="H166" s="12"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A167" s="13">
+      <c r="A167" s="7">
         <v>44105</v>
       </c>
-      <c r="B167" s="13">
+      <c r="B167" s="7">
         <v>44135</v>
       </c>
-      <c r="C167" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D167" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E167" s="16">
+      <c r="C167" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D167" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" s="13">
         <v>56.2</v>
       </c>
-      <c r="G167" s="16">
+      <c r="G167" s="13">
         <v>55.9</v>
       </c>
       <c r="H167" s="12"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A168" s="13">
+      <c r="A168" s="7">
         <v>44136</v>
       </c>
-      <c r="B168" s="13">
+      <c r="B168" s="7">
         <v>44165</v>
       </c>
-      <c r="C168" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D168" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E168" s="16">
+      <c r="C168" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E168" s="13">
         <v>56.4</v>
       </c>
-      <c r="F168" s="16">
+      <c r="F168" s="13">
         <v>56</v>
       </c>
-      <c r="G168" s="16">
+      <c r="G168" s="13">
         <v>56.2</v>
       </c>
       <c r="H168" s="12"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A169" s="13">
+      <c r="A169" s="7">
         <v>44166</v>
       </c>
-      <c r="B169" s="13">
+      <c r="B169" s="7">
         <v>44196</v>
       </c>
-      <c r="C169" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D169" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E169" s="16">
+      <c r="C169" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D169" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E169" s="13">
         <v>55.7</v>
       </c>
-      <c r="G169" s="16">
+      <c r="G169" s="13">
         <v>56.4</v>
       </c>
       <c r="H169" s="12"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A170" s="13">
+      <c r="A170" s="7">
         <v>44197</v>
       </c>
-      <c r="B170" s="13">
+      <c r="B170" s="7">
         <v>44227</v>
       </c>
-      <c r="C170" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D170" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E170" s="16">
+      <c r="C170" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D170" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E170" s="13">
         <v>52.4</v>
       </c>
-      <c r="G170" s="16">
+      <c r="G170" s="13">
         <v>55.7</v>
       </c>
       <c r="H170" s="12"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A171" s="13">
+      <c r="A171" s="7">
         <v>44228</v>
       </c>
-      <c r="B171" s="13">
+      <c r="B171" s="7">
         <v>44255</v>
       </c>
-      <c r="C171" s="18">
+      <c r="C171" s="8">
         <v>0.625</v>
       </c>
-      <c r="D171" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E171" s="16">
+      <c r="D171" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E171" s="13">
         <v>51.4</v>
       </c>
-      <c r="G171" s="16">
+      <c r="G171" s="13">
         <v>52.4</v>
       </c>
       <c r="H171" s="12"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A172" s="13">
+      <c r="A172" s="7">
         <v>44256</v>
       </c>
-      <c r="B172" s="13">
+      <c r="B172" s="7">
         <v>44286</v>
       </c>
-      <c r="C172" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D172" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E172" s="16">
+      <c r="C172" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D172" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E172" s="13">
         <v>56.3</v>
       </c>
-      <c r="G172" s="16">
+      <c r="G172" s="13">
         <v>51.4</v>
       </c>
       <c r="H172" s="12"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A173" s="13">
+      <c r="A173" s="7">
         <v>44287</v>
       </c>
-      <c r="B173" s="13">
+      <c r="B173" s="7">
         <v>44316</v>
       </c>
-      <c r="C173" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D173" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E173" s="16">
+      <c r="C173" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D173" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E173" s="13">
         <v>54.9</v>
       </c>
-      <c r="G173" s="16">
+      <c r="G173" s="13">
         <v>56.3</v>
       </c>
       <c r="H173" s="12"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A174" s="13">
+      <c r="A174" s="7">
         <v>44317</v>
       </c>
-      <c r="B174" s="13">
+      <c r="B174" s="7">
         <v>44347</v>
       </c>
-      <c r="C174" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D174" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E174" s="16">
+      <c r="C174" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D174" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E174" s="13">
         <v>55.2</v>
       </c>
-      <c r="G174" s="16">
+      <c r="G174" s="13">
         <v>54.9</v>
       </c>
       <c r="H174" s="12"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A175" s="13">
+      <c r="A175" s="7">
         <v>44348</v>
       </c>
-      <c r="B175" s="13">
+      <c r="B175" s="7">
         <v>44377</v>
       </c>
-      <c r="C175" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D175" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E175" s="16">
+      <c r="C175" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D175" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E175" s="13">
         <v>53.5</v>
       </c>
-      <c r="G175" s="16">
+      <c r="G175" s="13">
         <v>55.2</v>
       </c>
       <c r="H175" s="12"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A176" s="13">
+      <c r="A176" s="7">
         <v>44378</v>
       </c>
-      <c r="B176" s="13">
+      <c r="B176" s="7">
         <v>44408</v>
       </c>
-      <c r="C176" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D176" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E176" s="16">
+      <c r="C176" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D176" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E176" s="13">
         <v>53.3</v>
       </c>
-      <c r="G176" s="16">
+      <c r="G176" s="13">
         <v>53.5</v>
       </c>
       <c r="H176" s="12"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A177" s="13">
+      <c r="A177" s="7">
         <v>44409</v>
       </c>
-      <c r="B177" s="13">
+      <c r="B177" s="7">
         <v>44439</v>
       </c>
-      <c r="C177" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D177" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E177" s="16">
+      <c r="C177" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D177" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E177" s="13">
         <v>47.5</v>
       </c>
-      <c r="G177" s="16">
+      <c r="G177" s="13">
         <v>53.3</v>
       </c>
       <c r="H177" s="12"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A178" s="13">
+      <c r="A178" s="7">
         <v>44440</v>
       </c>
-      <c r="B178" s="13">
+      <c r="B178" s="7">
         <v>44469</v>
       </c>
-      <c r="C178" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D178" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E178" s="16">
+      <c r="C178" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E178" s="13">
         <v>53.2</v>
       </c>
-      <c r="G178" s="16">
+      <c r="G178" s="13">
         <v>47.5</v>
       </c>
       <c r="H178" s="12"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A179" s="13">
+      <c r="A179" s="7">
         <v>44470</v>
       </c>
-      <c r="B179" s="13">
+      <c r="B179" s="7">
         <v>44500</v>
       </c>
-      <c r="C179" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D179" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E179" s="16">
+      <c r="C179" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D179" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E179" s="13">
         <v>52.4</v>
       </c>
-      <c r="G179" s="16">
+      <c r="G179" s="13">
         <v>53.2</v>
       </c>
       <c r="H179" s="12"/>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A180" s="13">
+      <c r="A180" s="7">
         <v>44501</v>
       </c>
-      <c r="B180" s="13">
+      <c r="B180" s="7">
         <v>44530</v>
       </c>
-      <c r="C180" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D180" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E180" s="16">
+      <c r="C180" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D180" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E180" s="13">
         <v>52.3</v>
       </c>
-      <c r="G180" s="16">
+      <c r="G180" s="13">
         <v>52.4</v>
       </c>
       <c r="H180" s="12"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A181" s="13">
+      <c r="A181" s="7">
         <v>44531</v>
       </c>
-      <c r="B181" s="13">
+      <c r="B181" s="7">
         <v>44561</v>
       </c>
-      <c r="C181" s="18">
-        <v>0.375</v>
-      </c>
-      <c r="D181" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E181" s="16">
+      <c r="C181" s="8">
+        <v>0.375</v>
+      </c>
+      <c r="D181" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" s="13">
         <v>52.7</v>
       </c>
-      <c r="F181" s="16">
+      <c r="F181" s="13">
         <v>52</v>
       </c>
-      <c r="G181" s="16">
+      <c r="G181" s="13">
         <v>52.3</v>
       </c>
       <c r="H181" s="12"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A182" s="13">
+      <c r="A182" s="7">
         <v>44562</v>
       </c>
-      <c r="B182" s="13">
+      <c r="B182" s="7">
         <v>44591</v>
       </c>
-      <c r="C182" s="18">
+      <c r="C182" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D182" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E182" s="16">
+      <c r="D182" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" s="13">
         <v>51.1</v>
       </c>
-      <c r="G182" s="16">
+      <c r="G182" s="13">
         <v>52.7</v>
       </c>
       <c r="H182" s="12"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A183" s="13">
+      <c r="A183" s="7">
         <v>44593</v>
       </c>
-      <c r="B183" s="13">
+      <c r="B183" s="7">
         <v>44621</v>
       </c>
-      <c r="C183" s="18">
+      <c r="C183" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D183" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E183" s="16">
+      <c r="D183" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" s="13">
         <v>51.6</v>
       </c>
-      <c r="G183" s="16">
+      <c r="G183" s="13">
         <v>51.1</v>
       </c>
       <c r="H183" s="12"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A184" s="13">
+      <c r="A184" s="7">
         <v>44621</v>
       </c>
-      <c r="B184" s="13">
+      <c r="B184" s="7">
         <v>44651</v>
       </c>
-      <c r="C184" s="18">
+      <c r="C184" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D184" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E184" s="16">
+      <c r="D184" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E184" s="13">
         <v>48.4</v>
       </c>
-      <c r="G184" s="16">
+      <c r="G184" s="13">
         <v>51.6</v>
       </c>
       <c r="H184" s="12"/>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A185" s="13">
+      <c r="A185" s="7">
         <v>44652</v>
       </c>
-      <c r="B185" s="13">
+      <c r="B185" s="7">
         <v>44681</v>
       </c>
-      <c r="C185" s="18">
+      <c r="C185" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D185" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E185" s="16">
+      <c r="D185" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E185" s="13">
         <v>41.9</v>
       </c>
-      <c r="G185" s="16">
+      <c r="G185" s="13">
         <v>48.4</v>
       </c>
       <c r="H185" s="12"/>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A186" s="13">
+      <c r="A186" s="7">
         <v>44682</v>
       </c>
-      <c r="B186" s="13">
+      <c r="B186" s="7">
         <v>44712</v>
       </c>
-      <c r="C186" s="18">
+      <c r="C186" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D186" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E186" s="16">
+      <c r="D186" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E186" s="13">
         <v>47.8</v>
       </c>
-      <c r="G186" s="16">
+      <c r="G186" s="13">
         <v>41.9</v>
       </c>
       <c r="H186" s="12"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A187" s="13">
+      <c r="A187" s="7">
         <v>44713</v>
       </c>
-      <c r="B187" s="13">
+      <c r="B187" s="7">
         <v>44742</v>
       </c>
-      <c r="C187" s="18">
+      <c r="C187" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D187" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E187" s="16">
+      <c r="D187" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" s="13">
         <v>54.7</v>
       </c>
-      <c r="G187" s="16">
+      <c r="G187" s="13">
         <v>47.8</v>
       </c>
       <c r="H187" s="12"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A188" s="13">
+      <c r="A188" s="7">
         <v>44743</v>
       </c>
-      <c r="B188" s="13">
+      <c r="B188" s="7">
         <v>44773</v>
       </c>
-      <c r="C188" s="18">
+      <c r="C188" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D188" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E188" s="16">
+      <c r="D188" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" s="13">
         <v>53.8</v>
       </c>
-      <c r="F188" s="16">
+      <c r="F188" s="13">
         <v>53.9</v>
       </c>
-      <c r="G188" s="16">
+      <c r="G188" s="13">
         <v>54.7</v>
       </c>
       <c r="H188" s="12"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A189" s="13">
+      <c r="A189" s="7">
         <v>44774</v>
       </c>
-      <c r="B189" s="13">
+      <c r="B189" s="7">
         <v>44804</v>
       </c>
-      <c r="C189" s="18">
+      <c r="C189" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D189" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E189" s="16">
+      <c r="D189" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E189" s="13">
         <v>52.6</v>
       </c>
-      <c r="G189" s="16">
+      <c r="G189" s="13">
         <v>53.8</v>
       </c>
       <c r="H189" s="12"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A190" s="13">
+      <c r="A190" s="7">
         <v>44805</v>
       </c>
-      <c r="B190" s="13">
+      <c r="B190" s="7">
         <v>44834</v>
       </c>
-      <c r="C190" s="18">
+      <c r="C190" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D190" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E190" s="16">
+      <c r="D190" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E190" s="13">
         <v>50.6</v>
       </c>
-      <c r="G190" s="16">
+      <c r="G190" s="13">
         <v>52.6</v>
       </c>
       <c r="H190" s="12"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A191" s="13">
+      <c r="A191" s="7">
         <v>44835</v>
       </c>
-      <c r="B191" s="13">
+      <c r="B191" s="7">
         <v>44865</v>
       </c>
-      <c r="C191" s="18">
+      <c r="C191" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D191" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E191" s="16">
+      <c r="D191" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E191" s="13">
         <v>48.7</v>
       </c>
-      <c r="F191" s="16">
+      <c r="F191" s="13">
         <v>50.2</v>
       </c>
-      <c r="G191" s="16">
+      <c r="G191" s="13">
         <v>50.6</v>
       </c>
       <c r="H191" s="12"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A192" s="13">
+      <c r="A192" s="7">
         <v>44866</v>
       </c>
-      <c r="B192" s="13">
+      <c r="B192" s="7">
         <v>44895</v>
       </c>
-      <c r="C192" s="18">
+      <c r="C192" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D192" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E192" s="16">
+      <c r="D192" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E192" s="13">
         <v>46.7</v>
       </c>
-      <c r="F192" s="16">
+      <c r="F192" s="13">
         <v>48</v>
       </c>
-      <c r="G192" s="16">
+      <c r="G192" s="13">
         <v>48.7</v>
       </c>
       <c r="H192" s="12"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A193" s="13">
+      <c r="A193" s="7">
         <v>44896</v>
       </c>
-      <c r="B193" s="13">
+      <c r="B193" s="7">
         <v>44926</v>
       </c>
-      <c r="C193" s="18">
+      <c r="C193" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D193" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E193" s="16">
+      <c r="D193" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E193" s="13">
         <v>41.6</v>
       </c>
-      <c r="G193" s="16">
+      <c r="G193" s="13">
         <v>46.7</v>
       </c>
       <c r="H193" s="12"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A194" s="13">
+      <c r="A194" s="7">
         <v>44927</v>
       </c>
-      <c r="B194" s="13">
+      <c r="B194" s="7">
         <v>44957</v>
       </c>
-      <c r="C194" s="18">
+      <c r="C194" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D194" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E194" s="16">
+      <c r="D194" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" s="13">
         <v>54.4</v>
       </c>
-      <c r="F194" s="16">
+      <c r="F194" s="13">
         <v>52</v>
       </c>
-      <c r="G194" s="16">
+      <c r="G194" s="13">
         <v>41.6</v>
       </c>
       <c r="H194" s="12"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A195" s="13">
+      <c r="A195" s="7">
         <v>44958</v>
       </c>
-      <c r="B195" s="13">
+      <c r="B195" s="7">
         <v>44986</v>
       </c>
-      <c r="C195" s="18">
+      <c r="C195" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D195" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E195" s="16">
+      <c r="D195" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E195" s="13">
         <v>56.3</v>
       </c>
-      <c r="F195" s="16">
+      <c r="F195" s="13">
         <v>55</v>
       </c>
-      <c r="G195" s="16">
+      <c r="G195" s="13">
         <v>54.4</v>
       </c>
       <c r="H195" s="12"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A196" s="13">
+      <c r="A196" s="7">
         <v>44986</v>
       </c>
-      <c r="B196" s="13">
+      <c r="B196" s="7">
         <v>45016</v>
       </c>
-      <c r="C196" s="18">
+      <c r="C196" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D196" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E196" s="16">
+      <c r="D196" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E196" s="13">
         <v>58.2</v>
       </c>
-      <c r="F196" s="16">
+      <c r="F196" s="13">
         <v>54.3</v>
       </c>
-      <c r="G196" s="16">
+      <c r="G196" s="13">
         <v>56.3</v>
       </c>
       <c r="H196" s="12"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A197" s="13">
+      <c r="A197" s="7">
         <v>45017</v>
       </c>
-      <c r="B197" s="13">
+      <c r="B197" s="7">
         <v>45046</v>
       </c>
-      <c r="C197" s="18">
+      <c r="C197" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D197" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E197" s="16">
+      <c r="D197" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" s="13">
         <v>56.4</v>
       </c>
-      <c r="F197" s="16">
+      <c r="F197" s="13">
         <v>57</v>
       </c>
-      <c r="G197" s="16">
+      <c r="G197" s="13">
         <v>58.2</v>
       </c>
       <c r="H197" s="12"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A198" s="13">
+      <c r="A198" s="7">
         <v>45047</v>
       </c>
-      <c r="B198" s="13">
+      <c r="B198" s="7">
         <v>45077</v>
       </c>
-      <c r="C198" s="18">
+      <c r="C198" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D198" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E198" s="16">
+      <c r="D198" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E198" s="13">
         <v>54.5</v>
       </c>
-      <c r="F198" s="16">
+      <c r="F198" s="13">
         <v>54.9</v>
       </c>
-      <c r="G198" s="16">
+      <c r="G198" s="13">
         <v>56.4</v>
       </c>
       <c r="H198" s="12"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A199" s="13">
+      <c r="A199" s="7">
         <v>45078</v>
       </c>
-      <c r="B199" s="13">
+      <c r="B199" s="7">
         <v>45107</v>
       </c>
-      <c r="C199" s="18">
+      <c r="C199" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D199" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E199" s="16">
+      <c r="D199" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" s="13">
         <v>53.2</v>
       </c>
-      <c r="F199" s="16">
+      <c r="F199" s="13">
         <v>53.7</v>
       </c>
-      <c r="G199" s="16">
+      <c r="G199" s="13">
         <v>54.5</v>
       </c>
       <c r="H199" s="12"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A200" s="13">
+      <c r="A200" s="7">
         <v>45108</v>
       </c>
-      <c r="B200" s="13">
+      <c r="B200" s="7">
         <v>45138</v>
       </c>
-      <c r="C200" s="18">
+      <c r="C200" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D200" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E200" s="16">
+      <c r="D200" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E200" s="13">
         <v>51.5</v>
       </c>
-      <c r="F200" s="16">
+      <c r="F200" s="13">
         <v>52.9</v>
       </c>
-      <c r="G200" s="16">
+      <c r="G200" s="13">
         <v>53.2</v>
       </c>
       <c r="H200" s="12"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A201" s="13">
+      <c r="A201" s="7">
         <v>45139</v>
       </c>
-      <c r="B201" s="13">
+      <c r="B201" s="7">
         <v>45169</v>
       </c>
-      <c r="C201" s="18">
+      <c r="C201" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D201" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E201" s="16">
+      <c r="D201" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E201" s="13">
         <v>51</v>
       </c>
-      <c r="F201" s="16">
+      <c r="F201" s="13">
         <v>51.1</v>
       </c>
-      <c r="G201" s="16">
+      <c r="G201" s="13">
         <v>51.5</v>
       </c>
       <c r="H201" s="12"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A202" s="13">
+      <c r="A202" s="7">
         <v>45170</v>
       </c>
-      <c r="B202" s="13">
+      <c r="B202" s="7">
         <v>45199</v>
       </c>
-      <c r="C202" s="18">
+      <c r="C202" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D202" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E202" s="16">
+      <c r="D202" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E202" s="13">
         <v>51.7</v>
       </c>
-      <c r="F202" s="16">
+      <c r="F202" s="13">
         <v>51.5</v>
       </c>
-      <c r="G202" s="16">
+      <c r="G202" s="13">
         <v>51</v>
       </c>
       <c r="H202" s="12"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A203" s="13">
+      <c r="A203" s="7">
         <v>45200</v>
       </c>
-      <c r="B203" s="13">
+      <c r="B203" s="7">
         <v>45230</v>
       </c>
-      <c r="C203" s="18">
+      <c r="C203" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D203" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E203" s="16">
+      <c r="D203" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E203" s="13">
         <v>50.6</v>
       </c>
-      <c r="F203" s="16">
+      <c r="F203" s="13">
         <v>51.8</v>
       </c>
-      <c r="G203" s="16">
+      <c r="G203" s="13">
         <v>51.7</v>
       </c>
       <c r="H203" s="12"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A204" s="13">
+      <c r="A204" s="7">
         <v>45231</v>
       </c>
-      <c r="B204" s="13">
+      <c r="B204" s="7">
         <v>45260</v>
       </c>
-      <c r="C204" s="18">
+      <c r="C204" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D204" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E204" s="16">
+      <c r="D204" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E204" s="13">
         <v>50.2</v>
       </c>
-      <c r="F204" s="16">
+      <c r="F204" s="13">
         <v>51.1</v>
       </c>
-      <c r="G204" s="16">
+      <c r="G204" s="13">
         <v>50.6</v>
       </c>
       <c r="H204" s="12"/>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A205" s="13">
+      <c r="A205" s="7">
         <v>45261</v>
       </c>
-      <c r="B205" s="13">
+      <c r="B205" s="7">
         <v>45291</v>
       </c>
-      <c r="C205" s="18">
+      <c r="C205" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D205" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E205" s="16">
+      <c r="D205" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E205" s="13">
         <v>50.4</v>
       </c>
-      <c r="F205" s="16">
+      <c r="F205" s="13">
         <v>50.5</v>
       </c>
-      <c r="G205" s="16">
+      <c r="G205" s="13">
         <v>50.2</v>
       </c>
       <c r="H205" s="12"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A206" s="13">
+      <c r="A206" s="7">
         <v>45292</v>
       </c>
-      <c r="B206" s="13">
+      <c r="B206" s="7">
         <v>45322</v>
       </c>
-      <c r="C206" s="18">
+      <c r="C206" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D206" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E206" s="16">
+      <c r="D206" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" s="13">
         <v>50.7</v>
       </c>
-      <c r="F206" s="16">
+      <c r="F206" s="13">
         <v>50.6</v>
       </c>
-      <c r="G206" s="16">
+      <c r="G206" s="13">
         <v>50.4</v>
       </c>
       <c r="H206" s="12"/>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A207" s="13">
+      <c r="A207" s="7">
         <v>45323</v>
       </c>
-      <c r="B207" s="13">
+      <c r="B207" s="7">
         <v>45352</v>
       </c>
-      <c r="C207" s="18">
+      <c r="C207" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D207" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E207" s="16">
+      <c r="D207" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E207" s="13">
         <v>51.4</v>
       </c>
-      <c r="F207" s="16">
+      <c r="F207" s="13">
         <v>50.9</v>
       </c>
-      <c r="G207" s="16">
+      <c r="G207" s="13">
         <v>50.7</v>
       </c>
       <c r="H207" s="12"/>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A208" s="13">
+      <c r="A208" s="7">
         <v>45352</v>
       </c>
-      <c r="B208" s="13">
+      <c r="B208" s="7">
         <v>45382</v>
       </c>
-      <c r="C208" s="18">
+      <c r="C208" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D208" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E208" s="16">
+      <c r="D208" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E208" s="13">
         <v>53</v>
       </c>
-      <c r="F208" s="16">
+      <c r="F208" s="13">
         <v>51.3</v>
       </c>
-      <c r="G208" s="16">
+      <c r="G208" s="13">
         <v>51.4</v>
       </c>
       <c r="H208" s="12"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A209" s="13">
+      <c r="A209" s="7">
         <v>45383</v>
       </c>
-      <c r="B209" s="13">
+      <c r="B209" s="7">
         <v>45412</v>
       </c>
-      <c r="C209" s="18">
+      <c r="C209" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D209" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E209" s="16">
+      <c r="D209" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E209" s="13">
         <v>51.2</v>
       </c>
-      <c r="F209" s="16">
+      <c r="F209" s="13">
         <v>52.3</v>
       </c>
-      <c r="G209" s="16">
+      <c r="G209" s="13">
         <v>53</v>
       </c>
       <c r="H209" s="12"/>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A210" s="13">
+      <c r="A210" s="7">
         <v>45413</v>
       </c>
-      <c r="B210" s="13">
+      <c r="B210" s="7">
         <v>45443</v>
       </c>
-      <c r="C210" s="18">
+      <c r="C210" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D210" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E210" s="16">
+      <c r="D210" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E210" s="13">
         <v>51.1</v>
       </c>
-      <c r="F210" s="16">
+      <c r="F210" s="13">
         <v>51.5</v>
       </c>
-      <c r="G210" s="16">
+      <c r="G210" s="13">
         <v>51.2</v>
       </c>
       <c r="H210" s="12"/>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A211" s="13">
+      <c r="A211" s="7">
         <v>45444</v>
       </c>
-      <c r="B211" s="13">
+      <c r="B211" s="7">
         <v>45473</v>
       </c>
-      <c r="C211" s="18">
+      <c r="C211" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D211" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E211" s="16">
+      <c r="D211" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E211" s="13">
         <v>50.5</v>
       </c>
-      <c r="F211" s="16">
+      <c r="F211" s="13">
         <v>51.1</v>
       </c>
-      <c r="G211" s="16">
+      <c r="G211" s="13">
         <v>51.1</v>
       </c>
       <c r="H211" s="12"/>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A212" s="13">
+      <c r="A212" s="7">
         <v>45474</v>
       </c>
-      <c r="B212" s="13">
+      <c r="B212" s="7">
         <v>45504</v>
       </c>
-      <c r="C212" s="18">
+      <c r="C212" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D212" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E212" s="16">
+      <c r="D212" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" s="13">
         <v>50.2</v>
       </c>
-      <c r="F212" s="16">
+      <c r="F212" s="13">
         <v>50.3</v>
       </c>
-      <c r="G212" s="16">
+      <c r="G212" s="13">
         <v>50.5</v>
       </c>
       <c r="H212" s="12"/>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A213" s="13">
+      <c r="A213" s="7">
         <v>45505</v>
       </c>
-      <c r="B213" s="13">
+      <c r="B213" s="7">
         <v>45535</v>
       </c>
-      <c r="C213" s="18">
+      <c r="C213" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D213" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E213" s="16">
+      <c r="D213" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E213" s="13">
         <v>50.3</v>
       </c>
-      <c r="F213" s="16">
+      <c r="F213" s="13">
         <v>50</v>
       </c>
-      <c r="G213" s="16">
+      <c r="G213" s="13">
         <v>50.2</v>
       </c>
       <c r="H213" s="12"/>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A214" s="13">
+      <c r="A214" s="7">
         <v>45536</v>
       </c>
-      <c r="B214" s="13">
+      <c r="B214" s="7">
         <v>45565</v>
       </c>
-      <c r="C214" s="18">
+      <c r="C214" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D214" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E214" s="16">
+      <c r="D214" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E214" s="13">
         <v>50</v>
       </c>
-      <c r="F214" s="16">
+      <c r="F214" s="13">
         <v>50.4</v>
       </c>
-      <c r="G214" s="16">
+      <c r="G214" s="13">
         <v>50.3</v>
       </c>
       <c r="H214" s="12"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A215" s="13">
+      <c r="A215" s="7">
         <v>45566</v>
       </c>
-      <c r="B215" s="13">
+      <c r="B215" s="7">
         <v>45596</v>
       </c>
-      <c r="C215" s="18">
+      <c r="C215" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D215" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E215" s="16">
+      <c r="D215" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" s="13">
         <v>50.2</v>
       </c>
-      <c r="F215" s="16">
+      <c r="F215" s="13">
         <v>50.4</v>
       </c>
-      <c r="G215" s="16">
+      <c r="G215" s="13">
         <v>50</v>
       </c>
       <c r="H215" s="12"/>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A216" s="13">
+      <c r="A216" s="7">
         <v>45597</v>
       </c>
-      <c r="B216" s="13">
+      <c r="B216" s="7">
         <v>45626</v>
       </c>
-      <c r="C216" s="18">
+      <c r="C216" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D216" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E216" s="16">
+      <c r="D216" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E216" s="13">
         <v>50</v>
       </c>
-      <c r="F216" s="16">
+      <c r="F216" s="13">
         <v>50.4</v>
       </c>
-      <c r="G216" s="16">
+      <c r="G216" s="13">
         <v>50.2</v>
       </c>
       <c r="H216" s="12"/>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A217" s="13">
+      <c r="A217" s="7">
         <v>45627</v>
       </c>
-      <c r="B217" s="13">
+      <c r="B217" s="7">
         <v>45657</v>
       </c>
-      <c r="C217" s="18">
+      <c r="C217" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D217" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E217" s="16">
+      <c r="D217" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E217" s="13">
         <v>52.2</v>
       </c>
-      <c r="F217" s="16">
+      <c r="F217" s="13">
         <v>50.2</v>
       </c>
-      <c r="G217" s="16">
+      <c r="G217" s="13">
         <v>50</v>
       </c>
       <c r="H217" s="12"/>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A218" s="13">
+      <c r="A218" s="7">
         <v>45658</v>
       </c>
-      <c r="B218" s="13">
+      <c r="B218" s="7">
         <v>45684</v>
       </c>
-      <c r="C218" s="18">
+      <c r="C218" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D218" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E218" s="16">
+      <c r="D218" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E218" s="13">
         <v>50.2</v>
       </c>
-      <c r="G218" s="16">
+      <c r="G218" s="13">
         <v>52.2</v>
       </c>
       <c r="H218" s="12"/>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A219" s="13">
+      <c r="A219" s="7">
         <v>45689</v>
       </c>
-      <c r="B219" s="13">
+      <c r="B219" s="7">
         <v>45717</v>
       </c>
-      <c r="C219" s="18">
+      <c r="C219" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D219" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E219" s="16">
+      <c r="D219" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E219" s="13">
         <v>50.4</v>
       </c>
-      <c r="F219" s="16">
+      <c r="F219" s="13">
         <v>50.3</v>
       </c>
-      <c r="G219" s="16">
+      <c r="G219" s="13">
         <v>50.2</v>
       </c>
       <c r="H219" s="12"/>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A220" s="13">
+      <c r="A220" s="7">
         <v>45717</v>
       </c>
-      <c r="B220" s="13">
+      <c r="B220" s="7">
         <v>45747</v>
       </c>
-      <c r="C220" s="18">
+      <c r="C220" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D220" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E220" s="16">
+      <c r="D220" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E220" s="13">
         <v>50.8</v>
       </c>
-      <c r="F220" s="16">
+      <c r="F220" s="13">
         <v>50.5</v>
       </c>
-      <c r="G220" s="16">
+      <c r="G220" s="13">
         <v>50.4</v>
       </c>
       <c r="H220" s="12"/>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A221" s="13">
+      <c r="A221" s="7">
         <v>45748</v>
       </c>
-      <c r="B221" s="13">
+      <c r="B221" s="7">
         <v>45777</v>
       </c>
-      <c r="C221" s="18">
+      <c r="C221" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D221" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E221" s="16">
+      <c r="D221" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221" s="13">
         <v>50.4</v>
       </c>
-      <c r="F221" s="16">
+      <c r="F221" s="13">
         <v>50.6</v>
       </c>
-      <c r="G221" s="16">
+      <c r="G221" s="13">
         <v>50.8</v>
       </c>
       <c r="H221" s="12"/>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A222" s="13">
+      <c r="A222" s="7">
         <v>45778</v>
       </c>
-      <c r="B222" s="13">
+      <c r="B222" s="7">
         <v>45808</v>
       </c>
-      <c r="C222" s="18">
+      <c r="C222" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D222" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E222" s="16">
+      <c r="D222" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E222" s="13">
         <v>50.3</v>
       </c>
-      <c r="F222" s="16">
+      <c r="F222" s="13">
         <v>50.6</v>
       </c>
-      <c r="G222" s="16">
+      <c r="G222" s="13">
         <v>50.4</v>
       </c>
       <c r="H222" s="12"/>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A223" s="13">
+      <c r="A223" s="7">
         <v>45809</v>
       </c>
-      <c r="B223" s="13">
+      <c r="B223" s="7">
         <v>45838</v>
       </c>
-      <c r="C223" s="18">
+      <c r="C223" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D223" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E223" s="16">
+      <c r="D223" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E223" s="13">
         <v>50.5</v>
       </c>
-      <c r="F223" s="16">
+      <c r="F223" s="13">
         <v>50.3</v>
       </c>
-      <c r="G223" s="16">
+      <c r="G223" s="13">
         <v>50.3</v>
       </c>
       <c r="H223" s="12"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A224" s="13">
+      <c r="A224" s="7">
         <v>45839</v>
       </c>
-      <c r="B224" s="13">
+      <c r="B224" s="7">
         <v>45869</v>
       </c>
-      <c r="C224" s="18">
+      <c r="C224" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D224" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E224" s="16">
+      <c r="D224" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E224" s="13">
         <v>50.1</v>
       </c>
-      <c r="F224" s="16">
+      <c r="F224" s="13">
         <v>50.3</v>
       </c>
-      <c r="G224" s="16">
+      <c r="G224" s="13">
         <v>50.5</v>
       </c>
       <c r="H224" s="12"/>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A225" s="13">
+      <c r="A225" s="7">
         <v>45870</v>
       </c>
-      <c r="B225" s="13">
+      <c r="B225" s="7">
         <v>45900</v>
       </c>
-      <c r="C225" s="18">
+      <c r="C225" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D225" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E225" s="16">
+      <c r="D225" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E225" s="13">
         <v>50.3</v>
       </c>
-      <c r="F225" s="16">
+      <c r="F225" s="13">
         <v>50.3</v>
       </c>
-      <c r="G225" s="16">
+      <c r="G225" s="13">
         <v>50.1</v>
       </c>
       <c r="H225" s="12"/>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A226" s="13">
+      <c r="A226" s="7">
         <v>45901</v>
       </c>
-      <c r="B226" s="13">
+      <c r="B226" s="7">
         <v>45930</v>
       </c>
-      <c r="C226" s="18">
+      <c r="C226" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D226" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E226" s="16">
+      <c r="D226" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E226" s="13">
         <v>50</v>
       </c>
-      <c r="F226" s="16">
+      <c r="F226" s="13">
         <v>50.3</v>
       </c>
-      <c r="G226" s="16">
+      <c r="G226" s="13">
         <v>50.3</v>
       </c>
       <c r="H226" s="12"/>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A227" s="13">
+      <c r="A227" s="7">
         <v>45931</v>
       </c>
-      <c r="B227" s="13">
+      <c r="B227" s="7">
         <v>45961</v>
       </c>
-      <c r="C227" s="18">
+      <c r="C227" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D227" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E227" s="16">
+      <c r="D227" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E227" s="13">
         <v>50.1</v>
       </c>
-      <c r="F227" s="16">
+      <c r="F227" s="13">
         <v>50.1</v>
       </c>
-      <c r="G227" s="16">
+      <c r="G227" s="13">
         <v>50</v>
       </c>
       <c r="H227" s="12"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A228" s="13">
+      <c r="A228" s="7">
         <v>45962</v>
       </c>
-      <c r="B228" s="13">
+      <c r="B228" s="7">
         <v>45991</v>
       </c>
-      <c r="C228" s="18">
+      <c r="C228" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D228" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E228" s="16">
+      <c r="D228" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E228" s="13">
         <v>49.5</v>
       </c>
-      <c r="F228" s="16">
+      <c r="F228" s="13">
         <v>50</v>
       </c>
-      <c r="G228" s="16">
+      <c r="G228" s="13">
         <v>50.1</v>
       </c>
       <c r="H228" s="12"/>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A229" s="13">
+      <c r="A229" s="7">
         <v>45992</v>
       </c>
-      <c r="B229" s="13">
+      <c r="B229" s="7">
         <v>46022</v>
       </c>
-      <c r="C229" s="18">
+      <c r="C229" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D229" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E229" s="16">
+      <c r="D229" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E229" s="13">
         <v>50.2</v>
       </c>
-      <c r="F229" s="16">
+      <c r="F229" s="13">
         <v>49.6</v>
       </c>
-      <c r="G229" s="16">
+      <c r="G229" s="13">
         <v>49.5</v>
       </c>
       <c r="H229" s="12"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A230" s="13">
+      <c r="A230" s="7">
         <v>46023</v>
       </c>
-      <c r="B230" s="13">
+      <c r="B230" s="7">
         <v>46053</v>
       </c>
-      <c r="C230" s="18">
+      <c r="C230" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D230" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E230" s="16">
+      <c r="D230" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E230" s="13">
         <v>49.4</v>
       </c>
-      <c r="F230" s="16">
+      <c r="F230" s="13">
         <v>50.3</v>
       </c>
-      <c r="G230" s="16">
+      <c r="G230" s="13">
         <v>50.2</v>
       </c>
       <c r="H230" s="12"/>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A231" s="13">
+      <c r="A231" s="7">
         <v>46054</v>
       </c>
-      <c r="B231" s="13">
+      <c r="B231" s="7">
         <v>46085</v>
       </c>
-      <c r="C231" s="18">
+      <c r="C231" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D231" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E231" s="16">
+      <c r="D231" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E231" s="13">
         <v>49.5</v>
       </c>
-      <c r="F231" s="16">
+      <c r="F231" s="13">
         <v>49.8</v>
       </c>
-      <c r="G231" s="16">
+      <c r="G231" s="13">
         <v>49.4</v>
       </c>
       <c r="H231" s="12"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A232" s="13">
+      <c r="A232" s="7">
         <v>46082</v>
       </c>
-      <c r="B232" s="13">
+      <c r="B232" s="7">
         <v>46112</v>
       </c>
-      <c r="C232" s="18">
+      <c r="C232" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D232" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E232" s="16">
+      <c r="D232" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E232" s="13">
         <v>50.1</v>
       </c>
-      <c r="F232" s="16">
+      <c r="F232" s="13">
         <v>49.9</v>
       </c>
-      <c r="G232" s="16">
+      <c r="G232" s="13">
         <v>49.5</v>
       </c>
       <c r="H232" s="12"/>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A233" s="13">
+      <c r="A233" s="7">
         <v>46113</v>
       </c>
-      <c r="B233" s="13">
+      <c r="B233" s="7">
         <v>46142</v>
       </c>
-      <c r="C233" s="18">
+      <c r="C233" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D233" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E233" s="16">
+      <c r="D233" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E233" s="13">
         <v>49.4</v>
       </c>
-      <c r="F233" s="16">
+      <c r="F233" s="13">
         <v>49.9</v>
       </c>
-      <c r="G233" s="16">
+      <c r="G233" s="13">
         <v>50.1</v>
       </c>
       <c r="H233" s="12"/>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A234" s="13">
+      <c r="A234" s="7">
         <v>46143</v>
       </c>
-      <c r="B234" s="13">
+      <c r="B234" s="7">
         <v>46173</v>
       </c>
-      <c r="C234" s="18">
+      <c r="C234" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D234" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="E234" s="16">
+      <c r="D234" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E234" s="13">
         <v>50.1</v>
       </c>
-      <c r="F234" s="16">
+      <c r="F234" s="13">
         <v>49.5</v>
       </c>
-      <c r="G234" s="16">
+      <c r="G234" s="13">
         <v>49.4</v>
       </c>
       <c r="H234" s="12"/>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A235" s="13">
+      <c r="A235" s="7">
         <v>46174</v>
       </c>
-      <c r="B235" s="13">
+      <c r="B235" s="7">
         <v>46203</v>
       </c>
-      <c r="C235" s="18">
+      <c r="C235" s="8">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D235" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="F235" s="16">
+      <c r="D235" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E235" s="13">
+        <v>50.2</v>
+      </c>
+      <c r="F235" s="13">
         <v>49.9</v>
       </c>
-      <c r="G235" s="16">
+      <c r="G235" s="13">
         <v>50.1</v>
       </c>
       <c r="H235" s="12"/>
@@ -11672,6 +11667,7 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G235">
     <sortCondition ref="B2:B235"/>
   </sortState>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -11679,9 +11675,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4443F9EE-BDA7-42C7-BB47-C54379F4610C}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.796875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B2" t="s">
         <v>8</v>
       </c>
@@ -11689,12 +11685,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.45">
       <c r="B4" t="s">
         <v>9</v>
       </c>

--- a/data_lake/macro/China/China PMI.xlsx
+++ b/data_lake/macro/China/China PMI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data_lake\macro\China\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/junghunlee/Desktop/Pycharm/FinancialData/data_lake/macro/China/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B43AFFC1-3416-4842-A358-54A2835B9CA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13FAFB6B-E420-1C40-9BD8-FD4CD31A5F59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
+    <workbookView xWindow="1080" yWindow="780" windowWidth="22400" windowHeight="20800" activeTab="2" xr2:uid="{4C7AFA9F-A9F7-4D4A-8224-91102ADA8910}"/>
   </bookViews>
   <sheets>
     <sheet name="CPMINDX" sheetId="1" r:id="rId1"/>
@@ -89,24 +89,24 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="179" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="166" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="_(* #,##0.0_);_(* \(#,##0.0\);_(* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -114,7 +114,7 @@
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -122,7 +122,7 @@
       <u/>
       <sz val="12"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -159,52 +159,52 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="178" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="20" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="179" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="5" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="180" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="5" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
-    <cellStyle name="쉼표" xfId="3" builtinId="3"/>
-    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
-    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
+    <cellStyle name="Comma" xfId="3" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -537,19 +537,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8641136A-8358-754A-BFC1-48B8F9996351}">
   <dimension ref="A1:G259"/>
-  <sheetFormatPr defaultColWidth="11.453125" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9.26953125" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.26953125" style="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" style="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="11" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7" style="10" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.6328125" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.90625" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="11.453125" style="6"/>
+    <col min="6" max="6" width="8.6640625" style="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.83203125" style="10" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="11.5" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -572,7 +572,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>38353</v>
       </c>
@@ -595,7 +595,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>38384</v>
       </c>
@@ -618,7 +618,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>38412</v>
       </c>
@@ -641,7 +641,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>38443</v>
       </c>
@@ -664,7 +664,7 @@
         <v>57.9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>38473</v>
       </c>
@@ -687,7 +687,7 @@
         <v>56.7</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>38504</v>
       </c>
@@ -710,7 +710,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>38534</v>
       </c>
@@ -733,7 +733,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>38565</v>
       </c>
@@ -756,7 +756,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>38596</v>
       </c>
@@ -779,7 +779,7 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>38626</v>
       </c>
@@ -802,7 +802,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>38657</v>
       </c>
@@ -825,7 +825,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>38687</v>
       </c>
@@ -848,7 +848,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>38718</v>
       </c>
@@ -871,7 +871,7 @@
         <v>54.3</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>38749</v>
       </c>
@@ -894,7 +894,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>38777</v>
       </c>
@@ -917,7 +917,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>38808</v>
       </c>
@@ -940,7 +940,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>38838</v>
       </c>
@@ -963,7 +963,7 @@
         <v>58.1</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>38869</v>
       </c>
@@ -986,7 +986,7 @@
         <v>54.8</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>38899</v>
       </c>
@@ -1009,7 +1009,7 @@
         <v>54.1</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>38930</v>
       </c>
@@ -1032,7 +1032,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>38961</v>
       </c>
@@ -1055,7 +1055,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>38991</v>
       </c>
@@ -1078,7 +1078,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>39022</v>
       </c>
@@ -1101,7 +1101,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>39052</v>
       </c>
@@ -1124,7 +1124,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>39083</v>
       </c>
@@ -1147,7 +1147,7 @@
         <v>54.8</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>39114</v>
       </c>
@@ -1170,7 +1170,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>39142</v>
       </c>
@@ -1193,7 +1193,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>39173</v>
       </c>
@@ -1216,7 +1216,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>39203</v>
       </c>
@@ -1239,7 +1239,7 @@
         <v>58.6</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
         <v>39234</v>
       </c>
@@ -1262,7 +1262,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>39264</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>54.5</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>39295</v>
       </c>
@@ -1308,7 +1308,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>39326</v>
       </c>
@@ -1331,7 +1331,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>39356</v>
       </c>
@@ -1354,7 +1354,7 @@
         <v>56.1</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>39387</v>
       </c>
@@ -1377,7 +1377,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <v>39417</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>55.4</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>39448</v>
       </c>
@@ -1423,7 +1423,7 @@
         <v>55.3</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>39479</v>
       </c>
@@ -1446,7 +1446,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>39508</v>
       </c>
@@ -1469,7 +1469,7 @@
         <v>53.4</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>39539</v>
       </c>
@@ -1492,7 +1492,7 @@
         <v>58.4</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>39569</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>59.2</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>39600</v>
       </c>
@@ -1538,7 +1538,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>39630</v>
       </c>
@@ -1561,7 +1561,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
         <v>39661</v>
       </c>
@@ -1584,7 +1584,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>39692</v>
       </c>
@@ -1607,7 +1607,7 @@
         <v>48.4</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>39722</v>
       </c>
@@ -1630,7 +1630,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>39753</v>
       </c>
@@ -1653,7 +1653,7 @@
         <v>44.6</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
         <v>39783</v>
       </c>
@@ -1676,7 +1676,7 @@
         <v>38.799999999999997</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>39814</v>
       </c>
@@ -1699,7 +1699,7 @@
         <v>41.2</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
         <v>39845</v>
       </c>
@@ -1722,7 +1722,7 @@
         <v>45.3</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>39873</v>
       </c>
@@ -1745,7 +1745,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A53" s="7">
         <v>39904</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>39934</v>
       </c>
@@ -1791,7 +1791,7 @@
         <v>53.5</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A55" s="7">
         <v>39965</v>
       </c>
@@ -1814,7 +1814,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>39995</v>
       </c>
@@ -1837,7 +1837,7 @@
         <v>53.2</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A57" s="7">
         <v>40026</v>
       </c>
@@ -1860,7 +1860,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>40057</v>
       </c>
@@ -1883,7 +1883,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A59" s="7">
         <v>40087</v>
       </c>
@@ -1906,7 +1906,7 @@
         <v>54.3</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>40118</v>
       </c>
@@ -1929,7 +1929,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A61" s="7">
         <v>40148</v>
       </c>
@@ -1952,7 +1952,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>40179</v>
       </c>
@@ -1975,7 +1975,7 @@
         <v>56.6</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A63" s="7">
         <v>40210</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>40238</v>
       </c>
@@ -2021,7 +2021,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" s="7">
         <v>40269</v>
       </c>
@@ -2044,7 +2044,7 @@
         <v>55.1</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="7">
         <v>40299</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>55.7</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="7">
         <v>40330</v>
       </c>
@@ -2090,7 +2090,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="7">
         <v>40360</v>
       </c>
@@ -2113,7 +2113,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="7">
         <v>40391</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="7">
         <v>40422</v>
       </c>
@@ -2159,7 +2159,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="7">
         <v>40452</v>
       </c>
@@ -2182,7 +2182,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" s="7">
         <v>40483</v>
       </c>
@@ -2205,7 +2205,7 @@
         <v>54.7</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" s="7">
         <v>40513</v>
       </c>
@@ -2228,7 +2228,7 @@
         <v>55.2</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" s="7">
         <v>40544</v>
       </c>
@@ -2251,7 +2251,7 @@
         <v>53.9</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="7">
         <v>40575</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="7">
         <v>40603</v>
       </c>
@@ -2297,7 +2297,7 @@
         <v>52.2</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="7">
         <v>40634</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>53.4</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
         <v>40664</v>
       </c>
@@ -2343,7 +2343,7 @@
         <v>52.9</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" s="7">
         <v>40695</v>
       </c>
@@ -2366,7 +2366,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" s="7">
         <v>40725</v>
       </c>
@@ -2389,7 +2389,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A81" s="7">
         <v>40756</v>
       </c>
@@ -2412,7 +2412,7 @@
         <v>50.7</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A82" s="7">
         <v>40787</v>
       </c>
@@ -2435,7 +2435,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A83" s="7">
         <v>40817</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A84" s="7">
         <v>40848</v>
       </c>
@@ -2481,7 +2481,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A85" s="7">
         <v>40878</v>
       </c>
@@ -2504,7 +2504,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A86" s="7">
         <v>40909</v>
       </c>
@@ -2527,7 +2527,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A87" s="7">
         <v>40940</v>
       </c>
@@ -2550,7 +2550,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A88" s="7">
         <v>40969</v>
       </c>
@@ -2573,7 +2573,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A89" s="7">
         <v>41000</v>
       </c>
@@ -2596,7 +2596,7 @@
         <v>53.1</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A90" s="7">
         <v>41030</v>
       </c>
@@ -2619,7 +2619,7 @@
         <v>53.3</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A91" s="7">
         <v>41061</v>
       </c>
@@ -2642,7 +2642,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A92" s="7">
         <v>41091</v>
       </c>
@@ -2665,7 +2665,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A93" s="7">
         <v>41122</v>
       </c>
@@ -2688,7 +2688,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A94" s="7">
         <v>41153</v>
       </c>
@@ -2711,7 +2711,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A95" s="7">
         <v>41183</v>
       </c>
@@ -2734,7 +2734,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
         <v>41214</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <v>41244</v>
       </c>
@@ -2780,7 +2780,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <v>41275</v>
       </c>
@@ -2803,7 +2803,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <v>41306</v>
       </c>
@@ -2826,7 +2826,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <v>41334</v>
       </c>
@@ -2849,7 +2849,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <v>41365</v>
       </c>
@@ -2872,7 +2872,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <v>41395</v>
       </c>
@@ -2895,7 +2895,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <v>41426</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <v>41456</v>
       </c>
@@ -2941,7 +2941,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <v>41487</v>
       </c>
@@ -2964,7 +2964,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <v>41518</v>
       </c>
@@ -2987,7 +2987,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <v>41548</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <v>41579</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <v>41609</v>
       </c>
@@ -3056,7 +3056,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <v>41640</v>
       </c>
@@ -3079,7 +3079,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <v>41671</v>
       </c>
@@ -3102,7 +3102,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <v>41699</v>
       </c>
@@ -3125,7 +3125,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A113" s="7">
         <v>41730</v>
       </c>
@@ -3148,7 +3148,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A114" s="7">
         <v>41760</v>
       </c>
@@ -3171,7 +3171,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A115" s="7">
         <v>41791</v>
       </c>
@@ -3194,7 +3194,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A116" s="7">
         <v>41821</v>
       </c>
@@ -3217,7 +3217,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A117" s="7">
         <v>41852</v>
       </c>
@@ -3240,7 +3240,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A118" s="7">
         <v>41883</v>
       </c>
@@ -3263,7 +3263,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A119" s="7">
         <v>41913</v>
       </c>
@@ -3286,7 +3286,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A120" s="7">
         <v>41944</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A121" s="7">
         <v>41974</v>
       </c>
@@ -3332,7 +3332,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A122" s="7">
         <v>42005</v>
       </c>
@@ -3355,7 +3355,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A123" s="7">
         <v>42036</v>
       </c>
@@ -3378,7 +3378,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A124" s="7">
         <v>42064</v>
       </c>
@@ -3401,7 +3401,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A125" s="7">
         <v>42095</v>
       </c>
@@ -3424,7 +3424,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A126" s="7">
         <v>42125</v>
       </c>
@@ -3447,7 +3447,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A127" s="7">
         <v>42156</v>
       </c>
@@ -3470,7 +3470,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A128" s="7">
         <v>42186</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A129" s="7">
         <v>42217</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A130" s="7">
         <v>42248</v>
       </c>
@@ -3539,7 +3539,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A131" s="7">
         <v>42278</v>
       </c>
@@ -3562,7 +3562,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A132" s="7">
         <v>42309</v>
       </c>
@@ -3585,7 +3585,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A133" s="7">
         <v>42339</v>
       </c>
@@ -3608,7 +3608,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A134" s="7">
         <v>42370</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A135" s="7">
         <v>42401</v>
       </c>
@@ -3654,7 +3654,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A136" s="7">
         <v>42430</v>
       </c>
@@ -3677,7 +3677,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A137" s="7">
         <v>42461</v>
       </c>
@@ -3700,7 +3700,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A138" s="7">
         <v>42491</v>
       </c>
@@ -3723,7 +3723,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A139" s="7">
         <v>42522</v>
       </c>
@@ -3746,7 +3746,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A140" s="7">
         <v>42552</v>
       </c>
@@ -3769,7 +3769,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A141" s="7">
         <v>42583</v>
       </c>
@@ -3792,7 +3792,7 @@
         <v>49.9</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A142" s="7">
         <v>42614</v>
       </c>
@@ -3815,7 +3815,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A143" s="7">
         <v>42644</v>
       </c>
@@ -3838,7 +3838,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A144" s="7">
         <v>42675</v>
       </c>
@@ -3861,7 +3861,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A145" s="7">
         <v>42705</v>
       </c>
@@ -3884,7 +3884,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A146" s="7">
         <v>42736</v>
       </c>
@@ -3907,7 +3907,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="7">
         <v>42767</v>
       </c>
@@ -3930,7 +3930,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="7">
         <v>42795</v>
       </c>
@@ -3953,7 +3953,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="7">
         <v>42826</v>
       </c>
@@ -3976,7 +3976,7 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="7">
         <v>42856</v>
       </c>
@@ -3999,7 +3999,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <v>42887</v>
       </c>
@@ -4022,7 +4022,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <v>42917</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <v>42948</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <v>42979</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>51.7</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <v>43009</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>52.4</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <v>43040</v>
       </c>
@@ -4137,7 +4137,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <v>43070</v>
       </c>
@@ -4160,7 +4160,7 @@
         <v>51.8</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <v>43101</v>
       </c>
@@ -4183,7 +4183,7 @@
         <v>51.6</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A159" s="7">
         <v>43132</v>
       </c>
@@ -4206,7 +4206,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A160" s="7">
         <v>43160</v>
       </c>
@@ -4229,7 +4229,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A161" s="7">
         <v>43191</v>
       </c>
@@ -4252,7 +4252,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A162" s="7">
         <v>43221</v>
       </c>
@@ -4275,7 +4275,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A163" s="7">
         <v>43252</v>
       </c>
@@ -4298,7 +4298,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A164" s="7">
         <v>43282</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A165" s="7">
         <v>43313</v>
       </c>
@@ -4344,7 +4344,7 @@
         <v>51.2</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A166" s="7">
         <v>43344</v>
       </c>
@@ -4367,7 +4367,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A167" s="7">
         <v>43374</v>
       </c>
@@ -4390,7 +4390,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A168" s="7">
         <v>43405</v>
       </c>
@@ -4413,7 +4413,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A169" s="7">
         <v>43435</v>
       </c>
@@ -4436,7 +4436,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A170" s="7">
         <v>43466</v>
       </c>
@@ -4459,7 +4459,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A171" s="7">
         <v>43497</v>
       </c>
@@ -4482,7 +4482,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A172" s="7">
         <v>43525</v>
       </c>
@@ -4505,7 +4505,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <v>43556</v>
       </c>
@@ -4528,7 +4528,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <v>43586</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <v>43617</v>
       </c>
@@ -4574,7 +4574,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <v>43647</v>
       </c>
@@ -4597,7 +4597,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <v>43678</v>
       </c>
@@ -4620,7 +4620,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <v>43709</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <v>43739</v>
       </c>
@@ -4666,7 +4666,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <v>43770</v>
       </c>
@@ -4689,7 +4689,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <v>43800</v>
       </c>
@@ -4712,7 +4712,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <v>43831</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <v>43862</v>
       </c>
@@ -4758,7 +4758,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <v>43891</v>
       </c>
@@ -4781,7 +4781,7 @@
         <v>35.700000000000003</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A185" s="7">
         <v>43922</v>
       </c>
@@ -4804,7 +4804,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A186" s="7">
         <v>43952</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A187" s="7">
         <v>43983</v>
       </c>
@@ -4850,7 +4850,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A188" s="7">
         <v>44013</v>
       </c>
@@ -4873,7 +4873,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A189" s="7">
         <v>44044</v>
       </c>
@@ -4896,7 +4896,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A190" s="7">
         <v>44075</v>
       </c>
@@ -4919,7 +4919,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A191" s="7">
         <v>44105</v>
       </c>
@@ -4942,7 +4942,7 @@
         <v>51.5</v>
       </c>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A192" s="7">
         <v>44136</v>
       </c>
@@ -4965,7 +4965,7 @@
         <v>51.4</v>
       </c>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A193" s="7">
         <v>44166</v>
       </c>
@@ -4988,7 +4988,7 @@
         <v>52.1</v>
       </c>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A194" s="7">
         <v>44197</v>
       </c>
@@ -5011,7 +5011,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A195" s="7">
         <v>44228</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>51.3</v>
       </c>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A196" s="7">
         <v>44256</v>
       </c>
@@ -5057,7 +5057,7 @@
         <v>50.6</v>
       </c>
     </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A197" s="7">
         <v>44287</v>
       </c>
@@ -5080,7 +5080,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A198" s="7">
         <v>44317</v>
       </c>
@@ -5103,7 +5103,7 @@
         <v>51.1</v>
       </c>
     </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A199" s="7">
         <v>44348</v>
       </c>
@@ -5126,7 +5126,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A200" s="7">
         <v>44378</v>
       </c>
@@ -5149,7 +5149,7 @@
         <v>50.9</v>
       </c>
     </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A201" s="7">
         <v>44409</v>
       </c>
@@ -5172,7 +5172,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A202" s="7">
         <v>44440</v>
       </c>
@@ -5195,7 +5195,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A203" s="7">
         <v>44470</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A204" s="7">
         <v>44501</v>
       </c>
@@ -5241,7 +5241,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A205" s="7">
         <v>44531</v>
       </c>
@@ -5264,7 +5264,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A206" s="7">
         <v>44562</v>
       </c>
@@ -5287,7 +5287,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A207" s="7">
         <v>44593</v>
       </c>
@@ -5310,7 +5310,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <v>44621</v>
       </c>
@@ -5333,7 +5333,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A209" s="7">
         <v>44652</v>
       </c>
@@ -5356,7 +5356,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A210" s="7">
         <v>44682</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>47.4</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A211" s="7">
         <v>44713</v>
       </c>
@@ -5402,7 +5402,7 @@
         <v>49.6</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A212" s="7">
         <v>44743</v>
       </c>
@@ -5425,7 +5425,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A213" s="7">
         <v>44774</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A214" s="7">
         <v>44805</v>
       </c>
@@ -5471,7 +5471,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A215" s="7">
         <v>44835</v>
       </c>
@@ -5494,7 +5494,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A216" s="7">
         <v>44866</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A217" s="7">
         <v>44896</v>
       </c>
@@ -5540,7 +5540,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A218" s="7">
         <v>44927</v>
       </c>
@@ -5563,7 +5563,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A219" s="7">
         <v>44958</v>
       </c>
@@ -5586,7 +5586,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A220" s="7">
         <v>44986</v>
       </c>
@@ -5609,7 +5609,7 @@
         <v>52.6</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A221" s="7">
         <v>45017</v>
       </c>
@@ -5632,7 +5632,7 @@
         <v>51.9</v>
       </c>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A222" s="7">
         <v>45047</v>
       </c>
@@ -5655,7 +5655,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A223" s="7">
         <v>45078</v>
       </c>
@@ -5678,7 +5678,7 @@
         <v>48.8</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A224" s="7">
         <v>45108</v>
       </c>
@@ -5701,7 +5701,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A225" s="7">
         <v>45139</v>
       </c>
@@ -5724,7 +5724,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A226" s="7">
         <v>45170</v>
       </c>
@@ -5747,7 +5747,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A227" s="7">
         <v>45200</v>
       </c>
@@ -5770,7 +5770,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A228" s="7">
         <v>45231</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A229" s="7">
         <v>45261</v>
       </c>
@@ -5816,7 +5816,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A230" s="7">
         <v>45292</v>
       </c>
@@ -5839,7 +5839,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A231" s="7">
         <v>45323</v>
       </c>
@@ -5862,7 +5862,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A232" s="7">
         <v>45352</v>
       </c>
@@ -5885,7 +5885,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A233" s="7">
         <v>45383</v>
       </c>
@@ -5908,7 +5908,7 @@
         <v>50.8</v>
       </c>
     </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A234" s="7">
         <v>45413</v>
       </c>
@@ -5931,7 +5931,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A235" s="7">
         <v>45444</v>
       </c>
@@ -5954,7 +5954,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A236" s="7">
         <v>45474</v>
       </c>
@@ -5977,7 +5977,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A237" s="7">
         <v>45505</v>
       </c>
@@ -6000,7 +6000,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A238" s="7">
         <v>45536</v>
       </c>
@@ -6023,7 +6023,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A239" s="7">
         <v>45566</v>
       </c>
@@ -6046,7 +6046,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A240" s="7">
         <v>45597</v>
       </c>
@@ -6069,7 +6069,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A241" s="7">
         <v>45627</v>
       </c>
@@ -6092,7 +6092,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A242" s="7">
         <v>45658</v>
       </c>
@@ -6115,7 +6115,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A243" s="7">
         <v>45689</v>
       </c>
@@ -6138,7 +6138,7 @@
         <v>49.1</v>
       </c>
     </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A244" s="7">
         <v>45717</v>
       </c>
@@ -6161,7 +6161,7 @@
         <v>50.2</v>
       </c>
     </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A245" s="7">
         <v>45748</v>
       </c>
@@ -6184,7 +6184,7 @@
         <v>50.5</v>
       </c>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A246" s="7">
         <v>45778</v>
       </c>
@@ -6207,7 +6207,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A247" s="7">
         <v>45809</v>
       </c>
@@ -6230,7 +6230,7 @@
         <v>49.5</v>
       </c>
     </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A248" s="7">
         <v>45839</v>
       </c>
@@ -6253,7 +6253,7 @@
         <v>49.7</v>
       </c>
     </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A249" s="7">
         <v>45870</v>
       </c>
@@ -6276,7 +6276,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A250" s="7">
         <v>45901</v>
       </c>
@@ -6299,7 +6299,7 @@
         <v>49.4</v>
       </c>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A251" s="7">
         <v>45931</v>
       </c>
@@ -6322,7 +6322,7 @@
         <v>49.8</v>
       </c>
     </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A252" s="7">
         <v>45962</v>
       </c>
@@ -6345,7 +6345,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A253" s="7">
         <v>45992</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>49.2</v>
       </c>
     </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A254" s="7">
         <v>46023</v>
       </c>
@@ -6391,7 +6391,7 @@
         <v>50.1</v>
       </c>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A255" s="7">
         <v>46054</v>
       </c>
@@ -6414,7 +6414,7 @@
         <v>49.3</v>
       </c>
     </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A256" s="7">
         <v>46082</v>
       </c>
@@ -6437,7 +6437,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A257" s="7">
         <v>46113</v>
       </c>
@@ -6460,7 +6460,7 @@
         <v>50.4</v>
       </c>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A258" s="7">
         <v>46143</v>
       </c>
@@ -6483,7 +6483,7 @@
         <v>50.3</v>
       </c>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A259" s="7">
         <v>46174</v>
       </c>
@@ -6519,18 +6519,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{317C4CC0-835B-4324-B0A5-C9431E0655E3}">
   <dimension ref="A1:H235"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.08984375" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.7265625" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" style="8" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1796875" style="11" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="8.81640625" style="13"/>
-    <col min="8" max="8" width="9.08984375" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.7265625" style="6"/>
+    <col min="1" max="1" width="10.1640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" style="7" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.83203125" style="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="8.83203125" style="13"/>
+    <col min="8" max="8" width="9.1640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.6640625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
@@ -6554,7 +6554,7 @@
       </c>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="7">
         <v>39083</v>
       </c>
@@ -6572,7 +6572,7 @@
       </c>
       <c r="H2" s="12"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="7">
         <v>39114</v>
       </c>
@@ -6593,7 +6593,7 @@
       </c>
       <c r="H3" s="12"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="7">
         <v>39142</v>
       </c>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="H4" s="12"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>39173</v>
       </c>
@@ -6635,7 +6635,7 @@
       </c>
       <c r="H5" s="12"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>39203</v>
       </c>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="H6" s="12"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>39234</v>
       </c>
@@ -6677,7 +6677,7 @@
       </c>
       <c r="H7" s="12"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>39264</v>
       </c>
@@ -6698,7 +6698,7 @@
       </c>
       <c r="H8" s="12"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>39295</v>
       </c>
@@ -6719,7 +6719,7 @@
       </c>
       <c r="H9" s="12"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>39326</v>
       </c>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="H10" s="12"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="7">
         <v>39356</v>
       </c>
@@ -6761,7 +6761,7 @@
       </c>
       <c r="H11" s="12"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="7">
         <v>39387</v>
       </c>
@@ -6782,7 +6782,7 @@
       </c>
       <c r="H12" s="12"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="7">
         <v>39417</v>
       </c>
@@ -6803,7 +6803,7 @@
       </c>
       <c r="H13" s="12"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="7">
         <v>39448</v>
       </c>
@@ -6824,7 +6824,7 @@
       </c>
       <c r="H14" s="12"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="7">
         <v>39479</v>
       </c>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="H15" s="12"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="7">
         <v>39508</v>
       </c>
@@ -6866,7 +6866,7 @@
       </c>
       <c r="H16" s="12"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="7">
         <v>39539</v>
       </c>
@@ -6887,7 +6887,7 @@
       </c>
       <c r="H17" s="12"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="7">
         <v>39569</v>
       </c>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="H18" s="12"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="7">
         <v>39600</v>
       </c>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="H19" s="12"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="7">
         <v>39630</v>
       </c>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="H20" s="12"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="7">
         <v>39661</v>
       </c>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="H21" s="12"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="7">
         <v>39692</v>
       </c>
@@ -6992,7 +6992,7 @@
       </c>
       <c r="H22" s="12"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="7">
         <v>39722</v>
       </c>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="H23" s="12"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="7">
         <v>39753</v>
       </c>
@@ -7034,7 +7034,7 @@
       </c>
       <c r="H24" s="12"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="7">
         <v>39783</v>
       </c>
@@ -7055,7 +7055,7 @@
       </c>
       <c r="H25" s="12"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="7">
         <v>39814</v>
       </c>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H26" s="12"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="7">
         <v>39845</v>
       </c>
@@ -7097,7 +7097,7 @@
       </c>
       <c r="H27" s="12"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="7">
         <v>39873</v>
       </c>
@@ -7118,7 +7118,7 @@
       </c>
       <c r="H28" s="12"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="7">
         <v>39904</v>
       </c>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="H29" s="12"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="7">
         <v>39934</v>
       </c>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="H30" s="12"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="7">
         <v>39965</v>
       </c>
@@ -7181,7 +7181,7 @@
       </c>
       <c r="H31" s="12"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="7">
         <v>39995</v>
       </c>
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H32" s="12"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="7">
         <v>40026</v>
       </c>
@@ -7223,7 +7223,7 @@
       </c>
       <c r="H33" s="12"/>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="7">
         <v>40057</v>
       </c>
@@ -7244,7 +7244,7 @@
       </c>
       <c r="H34" s="12"/>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="7">
         <v>40087</v>
       </c>
@@ -7265,7 +7265,7 @@
       </c>
       <c r="H35" s="12"/>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="7">
         <v>40118</v>
       </c>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="H36" s="12"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="7">
         <v>40148</v>
       </c>
@@ -7307,7 +7307,7 @@
       </c>
       <c r="H37" s="12"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="7">
         <v>40179</v>
       </c>
@@ -7328,7 +7328,7 @@
       </c>
       <c r="H38" s="12"/>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="7">
         <v>40210</v>
       </c>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="H39" s="12"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="7">
         <v>40238</v>
       </c>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="H40" s="12"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="7">
         <v>40269</v>
       </c>
@@ -7391,7 +7391,7 @@
       </c>
       <c r="H41" s="12"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="7">
         <v>40299</v>
       </c>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="H42" s="12"/>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="7">
         <v>40330</v>
       </c>
@@ -7433,7 +7433,7 @@
       </c>
       <c r="H43" s="12"/>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="7">
         <v>40360</v>
       </c>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="H44" s="12"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="7">
         <v>40391</v>
       </c>
@@ -7475,7 +7475,7 @@
       </c>
       <c r="H45" s="12"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="7">
         <v>40422</v>
       </c>
@@ -7496,7 +7496,7 @@
       </c>
       <c r="H46" s="12"/>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="7">
         <v>40452</v>
       </c>
@@ -7517,7 +7517,7 @@
       </c>
       <c r="H47" s="12"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="7">
         <v>40483</v>
       </c>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="H48" s="12"/>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="7">
         <v>40513</v>
       </c>
@@ -7559,7 +7559,7 @@
       </c>
       <c r="H49" s="12"/>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="7">
         <v>40544</v>
       </c>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="H50" s="12"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="7">
         <v>40575</v>
       </c>
@@ -7601,7 +7601,7 @@
       </c>
       <c r="H51" s="12"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="7">
         <v>40603</v>
       </c>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="H52" s="12"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="7">
         <v>40634</v>
       </c>
@@ -7643,7 +7643,7 @@
       </c>
       <c r="H53" s="12"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="7">
         <v>40664</v>
       </c>
@@ -7664,7 +7664,7 @@
       </c>
       <c r="H54" s="12"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="7">
         <v>40695</v>
       </c>
@@ -7685,7 +7685,7 @@
       </c>
       <c r="H55" s="12"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="7">
         <v>40725</v>
       </c>
@@ -7706,7 +7706,7 @@
       </c>
       <c r="H56" s="12"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="7">
         <v>40756</v>
       </c>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="H57" s="12"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="7">
         <v>40787</v>
       </c>
@@ -7748,7 +7748,7 @@
       </c>
       <c r="H58" s="12"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="7">
         <v>40817</v>
       </c>
@@ -7769,7 +7769,7 @@
       </c>
       <c r="H59" s="12"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="7">
         <v>40848</v>
       </c>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="H60" s="12"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="7">
         <v>40878</v>
       </c>
@@ -7811,7 +7811,7 @@
       </c>
       <c r="H61" s="12"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="7">
         <v>40909</v>
       </c>
@@ -7832,7 +7832,7 @@
       </c>
       <c r="H62" s="12"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="7">
         <v>40940</v>
       </c>
@@ -7853,7 +7853,7 @@
       </c>
       <c r="H63" s="12"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="7">
         <v>40969</v>
       </c>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="H64" s="12"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="7">
         <v>41000</v>
       </c>
@@ -7895,7 +7895,7 @@
       </c>
       <c r="H65" s="12"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="7">
         <v>41030</v>
       </c>
@@ -7916,7 +7916,7 @@
       </c>
       <c r="H66" s="12"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="7">
         <v>41061</v>
       </c>
@@ -7937,7 +7937,7 @@
       </c>
       <c r="H67" s="12"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="7">
         <v>41091</v>
       </c>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="H68" s="12"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="7">
         <v>41122</v>
       </c>
@@ -7979,7 +7979,7 @@
       </c>
       <c r="H69" s="12"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="7">
         <v>41153</v>
       </c>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="H70" s="12"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="7">
         <v>41183</v>
       </c>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="H71" s="12"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="7">
         <v>41214</v>
       </c>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="H72" s="12"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="7">
         <v>41244</v>
       </c>
@@ -8063,7 +8063,7 @@
       </c>
       <c r="H73" s="12"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="7">
         <v>41275</v>
       </c>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="H74" s="12"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="7">
         <v>41306</v>
       </c>
@@ -8105,7 +8105,7 @@
       </c>
       <c r="H75" s="12"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="7">
         <v>41334</v>
       </c>
@@ -8126,7 +8126,7 @@
       </c>
       <c r="H76" s="12"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="7">
         <v>41365</v>
       </c>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="H77" s="12"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="7">
         <v>41395</v>
       </c>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="H78" s="12"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="7">
         <v>41426</v>
       </c>
@@ -8189,7 +8189,7 @@
       </c>
       <c r="H79" s="12"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="7">
         <v>41456</v>
       </c>
@@ -8210,7 +8210,7 @@
       </c>
       <c r="H80" s="12"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="7">
         <v>41487</v>
       </c>
@@ -8231,7 +8231,7 @@
       </c>
       <c r="H81" s="12"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="7">
         <v>41518</v>
       </c>
@@ -8252,7 +8252,7 @@
       </c>
       <c r="H82" s="12"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="7">
         <v>41548</v>
       </c>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="H83" s="12"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="7">
         <v>41579</v>
       </c>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="H84" s="12"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="7">
         <v>41609</v>
       </c>
@@ -8315,7 +8315,7 @@
       </c>
       <c r="H85" s="12"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="7">
         <v>41640</v>
       </c>
@@ -8336,7 +8336,7 @@
       </c>
       <c r="H86" s="12"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="7">
         <v>41671</v>
       </c>
@@ -8357,7 +8357,7 @@
       </c>
       <c r="H87" s="12"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="7">
         <v>41699</v>
       </c>
@@ -8378,7 +8378,7 @@
       </c>
       <c r="H88" s="12"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="7">
         <v>41730</v>
       </c>
@@ -8399,7 +8399,7 @@
       </c>
       <c r="H89" s="12"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="7">
         <v>41760</v>
       </c>
@@ -8420,7 +8420,7 @@
       </c>
       <c r="H90" s="12"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="7">
         <v>41791</v>
       </c>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="H91" s="12"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="7">
         <v>41821</v>
       </c>
@@ -8462,7 +8462,7 @@
       </c>
       <c r="H92" s="12"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="7">
         <v>41852</v>
       </c>
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H93" s="12"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="7">
         <v>41883</v>
       </c>
@@ -8504,7 +8504,7 @@
       </c>
       <c r="H94" s="12"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="7">
         <v>41913</v>
       </c>
@@ -8525,7 +8525,7 @@
       </c>
       <c r="H95" s="12"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="7">
         <v>41944</v>
       </c>
@@ -8546,7 +8546,7 @@
       </c>
       <c r="H96" s="12"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="7">
         <v>41974</v>
       </c>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="H97" s="12"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="7">
         <v>42005</v>
       </c>
@@ -8588,7 +8588,7 @@
       </c>
       <c r="H98" s="12"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="7">
         <v>42036</v>
       </c>
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H99" s="12"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="7">
         <v>42064</v>
       </c>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="H100" s="12"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="7">
         <v>42095</v>
       </c>
@@ -8651,7 +8651,7 @@
       </c>
       <c r="H101" s="12"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="7">
         <v>42125</v>
       </c>
@@ -8672,7 +8672,7 @@
       </c>
       <c r="H102" s="12"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="7">
         <v>42156</v>
       </c>
@@ -8693,7 +8693,7 @@
       </c>
       <c r="H103" s="12"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="7">
         <v>42186</v>
       </c>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="H104" s="12"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="7">
         <v>42217</v>
       </c>
@@ -8735,7 +8735,7 @@
       </c>
       <c r="H105" s="12"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="7">
         <v>42248</v>
       </c>
@@ -8756,7 +8756,7 @@
       </c>
       <c r="H106" s="12"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="7">
         <v>42278</v>
       </c>
@@ -8777,7 +8777,7 @@
       </c>
       <c r="H107" s="12"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="7">
         <v>42309</v>
       </c>
@@ -8798,7 +8798,7 @@
       </c>
       <c r="H108" s="12"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="7">
         <v>42339</v>
       </c>
@@ -8819,7 +8819,7 @@
       </c>
       <c r="H109" s="12"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="7">
         <v>42370</v>
       </c>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="H110" s="12"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="7">
         <v>42401</v>
       </c>
@@ -8861,7 +8861,7 @@
       </c>
       <c r="H111" s="12"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="7">
         <v>42430</v>
       </c>
@@ -8882,7 +8882,7 @@
       </c>
       <c r="H112" s="12"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="7">
         <v>42461</v>
       </c>
@@ -8903,7 +8903,7 @@
       </c>
       <c r="H113" s="12"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="7">
         <v>42491</v>
       </c>
@@ -8924,7 +8924,7 @@
       </c>
       <c r="H114" s="12"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="7">
         <v>42522</v>
       </c>
@@ -8945,7 +8945,7 @@
       </c>
       <c r="H115" s="12"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="7">
         <v>42552</v>
       </c>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="H116" s="12"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="7">
         <v>42583</v>
       </c>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="H117" s="12"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="7">
         <v>42614</v>
       </c>
@@ -9008,7 +9008,7 @@
       </c>
       <c r="H118" s="12"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="7">
         <v>42644</v>
       </c>
@@ -9029,7 +9029,7 @@
       </c>
       <c r="H119" s="12"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="7">
         <v>42675</v>
       </c>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="H120" s="12"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="7">
         <v>42705</v>
       </c>
@@ -9071,7 +9071,7 @@
       </c>
       <c r="H121" s="12"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="7">
         <v>42736</v>
       </c>
@@ -9092,7 +9092,7 @@
       </c>
       <c r="H122" s="12"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="7">
         <v>42767</v>
       </c>
@@ -9113,7 +9113,7 @@
       </c>
       <c r="H123" s="12"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="7">
         <v>42795</v>
       </c>
@@ -9134,7 +9134,7 @@
       </c>
       <c r="H124" s="12"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="7">
         <v>42826</v>
       </c>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="H125" s="12"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="7">
         <v>42856</v>
       </c>
@@ -9176,7 +9176,7 @@
       </c>
       <c r="H126" s="12"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="7">
         <v>42887</v>
       </c>
@@ -9197,7 +9197,7 @@
       </c>
       <c r="H127" s="12"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="7">
         <v>42917</v>
       </c>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="H128" s="12"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="7">
         <v>42948</v>
       </c>
@@ -9239,7 +9239,7 @@
       </c>
       <c r="H129" s="12"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="7">
         <v>42979</v>
       </c>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="H130" s="12"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="7">
         <v>43009</v>
       </c>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="H131" s="12"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="7">
         <v>43040</v>
       </c>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="H132" s="12"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="7">
         <v>43070</v>
       </c>
@@ -9323,7 +9323,7 @@
       </c>
       <c r="H133" s="12"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="7">
         <v>43101</v>
       </c>
@@ -9347,7 +9347,7 @@
       </c>
       <c r="H134" s="12"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="7">
         <v>43132</v>
       </c>
@@ -9371,7 +9371,7 @@
       </c>
       <c r="H135" s="12"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="7">
         <v>43160</v>
       </c>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="H136" s="12"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="7">
         <v>43191</v>
       </c>
@@ -9416,7 +9416,7 @@
       </c>
       <c r="H137" s="12"/>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="7">
         <v>43221</v>
       </c>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="H138" s="12"/>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="7">
         <v>43252</v>
       </c>
@@ -9464,7 +9464,7 @@
       </c>
       <c r="H139" s="12"/>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="7">
         <v>43282</v>
       </c>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="H140" s="12"/>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="7">
         <v>43313</v>
       </c>
@@ -9512,7 +9512,7 @@
       </c>
       <c r="H141" s="12"/>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="7">
         <v>43344</v>
       </c>
@@ -9533,7 +9533,7 @@
       </c>
       <c r="H142" s="12"/>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="7">
         <v>43374</v>
       </c>
@@ -9557,7 +9557,7 @@
       </c>
       <c r="H143" s="12"/>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="7">
         <v>43405</v>
       </c>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H144" s="12"/>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="7">
         <v>43435</v>
       </c>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="H145" s="12"/>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="7">
         <v>43466</v>
       </c>
@@ -9629,7 +9629,7 @@
       </c>
       <c r="H146" s="12"/>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="7">
         <v>43497</v>
       </c>
@@ -9653,7 +9653,7 @@
       </c>
       <c r="H147" s="12"/>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="7">
         <v>43525</v>
       </c>
@@ -9677,7 +9677,7 @@
       </c>
       <c r="H148" s="12"/>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="7">
         <v>43556</v>
       </c>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="H149" s="12"/>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="7">
         <v>43586</v>
       </c>
@@ -9725,7 +9725,7 @@
       </c>
       <c r="H150" s="12"/>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="7">
         <v>43617</v>
       </c>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="H151" s="12"/>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="7">
         <v>43647</v>
       </c>
@@ -9773,7 +9773,7 @@
       </c>
       <c r="H152" s="12"/>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="7">
         <v>43678</v>
       </c>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="H153" s="12"/>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="7">
         <v>43709</v>
       </c>
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" s="12"/>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="7">
         <v>43739</v>
       </c>
@@ -9845,7 +9845,7 @@
       </c>
       <c r="H155" s="12"/>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="7">
         <v>43770</v>
       </c>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="H156" s="12"/>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="7">
         <v>43800</v>
       </c>
@@ -9887,7 +9887,7 @@
       </c>
       <c r="H157" s="12"/>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="7">
         <v>43831</v>
       </c>
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H158" s="12"/>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="7">
         <v>43862</v>
       </c>
@@ -9929,7 +9929,7 @@
       </c>
       <c r="H159" s="12"/>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="7">
         <v>43891</v>
       </c>
@@ -9950,7 +9950,7 @@
       </c>
       <c r="H160" s="12"/>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="7">
         <v>43922</v>
       </c>
@@ -9971,7 +9971,7 @@
       </c>
       <c r="H161" s="12"/>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="7">
         <v>43952</v>
       </c>
@@ -9992,7 +9992,7 @@
       </c>
       <c r="H162" s="12"/>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="7">
         <v>43983</v>
       </c>
@@ -10013,7 +10013,7 @@
       </c>
       <c r="H163" s="12"/>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="7">
         <v>44013</v>
       </c>
@@ -10034,7 +10034,7 @@
       </c>
       <c r="H164" s="12"/>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="7">
         <v>44044</v>
       </c>
@@ -10055,7 +10055,7 @@
       </c>
       <c r="H165" s="12"/>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="7">
         <v>44075</v>
       </c>
@@ -10076,7 +10076,7 @@
       </c>
       <c r="H166" s="12"/>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="7">
         <v>44105</v>
       </c>
@@ -10097,7 +10097,7 @@
       </c>
       <c r="H167" s="12"/>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="7">
         <v>44136</v>
       </c>
@@ -10121,7 +10121,7 @@
       </c>
       <c r="H168" s="12"/>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="7">
         <v>44166</v>
       </c>
@@ -10142,7 +10142,7 @@
       </c>
       <c r="H169" s="12"/>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="7">
         <v>44197</v>
       </c>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="H170" s="12"/>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="7">
         <v>44228</v>
       </c>
@@ -10184,7 +10184,7 @@
       </c>
       <c r="H171" s="12"/>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="7">
         <v>44256</v>
       </c>
@@ -10205,7 +10205,7 @@
       </c>
       <c r="H172" s="12"/>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="7">
         <v>44287</v>
       </c>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="H173" s="12"/>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="7">
         <v>44317</v>
       </c>
@@ -10247,7 +10247,7 @@
       </c>
       <c r="H174" s="12"/>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="7">
         <v>44348</v>
       </c>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="H175" s="12"/>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="7">
         <v>44378</v>
       </c>
@@ -10289,7 +10289,7 @@
       </c>
       <c r="H176" s="12"/>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="7">
         <v>44409</v>
       </c>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="H177" s="12"/>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="7">
         <v>44440</v>
       </c>
@@ -10331,7 +10331,7 @@
       </c>
       <c r="H178" s="12"/>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="7">
         <v>44470</v>
       </c>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="H179" s="12"/>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="7">
         <v>44501</v>
       </c>
@@ -10373,7 +10373,7 @@
       </c>
       <c r="H180" s="12"/>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="7">
         <v>44531</v>
       </c>
@@ -10397,7 +10397,7 @@
       </c>
       <c r="H181" s="12"/>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="7">
         <v>44562</v>
       </c>
@@ -10418,7 +10418,7 @@
       </c>
       <c r="H182" s="12"/>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="7">
         <v>44593</v>
       </c>
@@ -10439,7 +10439,7 @@
       </c>
       <c r="H183" s="12"/>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="7">
         <v>44621</v>
       </c>
@@ -10460,7 +10460,7 @@
       </c>
       <c r="H184" s="12"/>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="7">
         <v>44652</v>
       </c>
@@ -10481,7 +10481,7 @@
       </c>
       <c r="H185" s="12"/>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="7">
         <v>44682</v>
       </c>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="H186" s="12"/>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="7">
         <v>44713</v>
       </c>
@@ -10523,7 +10523,7 @@
       </c>
       <c r="H187" s="12"/>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="7">
         <v>44743</v>
       </c>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="H188" s="12"/>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="7">
         <v>44774</v>
       </c>
@@ -10568,7 +10568,7 @@
       </c>
       <c r="H189" s="12"/>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="7">
         <v>44805</v>
       </c>
@@ -10589,7 +10589,7 @@
       </c>
       <c r="H190" s="12"/>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="7">
         <v>44835</v>
       </c>
@@ -10613,7 +10613,7 @@
       </c>
       <c r="H191" s="12"/>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="7">
         <v>44866</v>
       </c>
@@ -10637,7 +10637,7 @@
       </c>
       <c r="H192" s="12"/>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="7">
         <v>44896</v>
       </c>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="H193" s="12"/>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="7">
         <v>44927</v>
       </c>
@@ -10682,7 +10682,7 @@
       </c>
       <c r="H194" s="12"/>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="7">
         <v>44958</v>
       </c>
@@ -10706,7 +10706,7 @@
       </c>
       <c r="H195" s="12"/>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="7">
         <v>44986</v>
       </c>
@@ -10730,7 +10730,7 @@
       </c>
       <c r="H196" s="12"/>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="7">
         <v>45017</v>
       </c>
@@ -10754,7 +10754,7 @@
       </c>
       <c r="H197" s="12"/>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="7">
         <v>45047</v>
       </c>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="H198" s="12"/>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="7">
         <v>45078</v>
       </c>
@@ -10802,7 +10802,7 @@
       </c>
       <c r="H199" s="12"/>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="7">
         <v>45108</v>
       </c>
@@ -10826,7 +10826,7 @@
       </c>
       <c r="H200" s="12"/>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="7">
         <v>45139</v>
       </c>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="H201" s="12"/>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="7">
         <v>45170</v>
       </c>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="H202" s="12"/>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="7">
         <v>45200</v>
       </c>
@@ -10898,7 +10898,7 @@
       </c>
       <c r="H203" s="12"/>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="7">
         <v>45231</v>
       </c>
@@ -10922,7 +10922,7 @@
       </c>
       <c r="H204" s="12"/>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="7">
         <v>45261</v>
       </c>
@@ -10946,7 +10946,7 @@
       </c>
       <c r="H205" s="12"/>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="7">
         <v>45292</v>
       </c>
@@ -10970,7 +10970,7 @@
       </c>
       <c r="H206" s="12"/>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="7">
         <v>45323</v>
       </c>
@@ -10994,7 +10994,7 @@
       </c>
       <c r="H207" s="12"/>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="7">
         <v>45352</v>
       </c>
@@ -11018,7 +11018,7 @@
       </c>
       <c r="H208" s="12"/>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="7">
         <v>45383</v>
       </c>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="H209" s="12"/>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="7">
         <v>45413</v>
       </c>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="H210" s="12"/>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="7">
         <v>45444</v>
       </c>
@@ -11090,7 +11090,7 @@
       </c>
       <c r="H211" s="12"/>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="7">
         <v>45474</v>
       </c>
@@ -11114,7 +11114,7 @@
       </c>
       <c r="H212" s="12"/>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="7">
         <v>45505</v>
       </c>
@@ -11138,7 +11138,7 @@
       </c>
       <c r="H213" s="12"/>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="7">
         <v>45536</v>
       </c>
@@ -11162,7 +11162,7 @@
       </c>
       <c r="H214" s="12"/>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="7">
         <v>45566</v>
       </c>
@@ -11186,7 +11186,7 @@
       </c>
       <c r="H215" s="12"/>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="7">
         <v>45597</v>
       </c>
@@ -11210,7 +11210,7 @@
       </c>
       <c r="H216" s="12"/>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="7">
         <v>45627</v>
       </c>
@@ -11234,7 +11234,7 @@
       </c>
       <c r="H217" s="12"/>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="7">
         <v>45658</v>
       </c>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="H218" s="12"/>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="7">
         <v>45689</v>
       </c>
@@ -11279,7 +11279,7 @@
       </c>
       <c r="H219" s="12"/>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="7">
         <v>45717</v>
       </c>
@@ -11303,7 +11303,7 @@
       </c>
       <c r="H220" s="12"/>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="7">
         <v>45748</v>
       </c>
@@ -11327,7 +11327,7 @@
       </c>
       <c r="H221" s="12"/>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="7">
         <v>45778</v>
       </c>
@@ -11351,7 +11351,7 @@
       </c>
       <c r="H222" s="12"/>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="7">
         <v>45809</v>
       </c>
@@ -11375,7 +11375,7 @@
       </c>
       <c r="H223" s="12"/>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="7">
         <v>45839</v>
       </c>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="H224" s="12"/>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="7">
         <v>45870</v>
       </c>
@@ -11423,7 +11423,7 @@
       </c>
       <c r="H225" s="12"/>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="7">
         <v>45901</v>
       </c>
@@ -11447,7 +11447,7 @@
       </c>
       <c r="H226" s="12"/>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="7">
         <v>45931</v>
       </c>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="H227" s="12"/>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="7">
         <v>45962</v>
       </c>
@@ -11495,7 +11495,7 @@
       </c>
       <c r="H228" s="12"/>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="7">
         <v>45992</v>
       </c>
@@ -11519,7 +11519,7 @@
       </c>
       <c r="H229" s="12"/>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="7">
         <v>46023</v>
       </c>
@@ -11543,7 +11543,7 @@
       </c>
       <c r="H230" s="12"/>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="7">
         <v>46054</v>
       </c>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="H231" s="12"/>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="7">
         <v>46082</v>
       </c>
@@ -11591,7 +11591,7 @@
       </c>
       <c r="H232" s="12"/>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="7">
         <v>46113</v>
       </c>
@@ -11615,7 +11615,7 @@
       </c>
       <c r="H233" s="12"/>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="7">
         <v>46143</v>
       </c>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="H234" s="12"/>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="7">
         <v>46174</v>
       </c>
@@ -11675,9 +11675,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4443F9EE-BDA7-42C7-BB47-C54379F4610C}">
   <dimension ref="B2:C4"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="19.2" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="2" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B2" t="s">
         <v>8</v>
       </c>
@@ -11685,12 +11685,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:3" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="2:3" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>9</v>
       </c>
